--- a/output/version3/test/15-5/MARL/CTDE/RL-RL with EP/(RL+RL) test results.xlsx
+++ b/output/version3/test/15-5/MARL/CTDE/RL-RL with EP/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>618</v>
+        <v>653</v>
       </c>
       <c r="C2" t="n">
+        <v>591</v>
+      </c>
+      <c r="D2" t="n">
+        <v>661</v>
+      </c>
+      <c r="E2" t="n">
         <v>607</v>
       </c>
-      <c r="D2" t="n">
-        <v>614</v>
-      </c>
-      <c r="E2" t="n">
-        <v>744</v>
-      </c>
       <c r="F2" t="n">
-        <v>672</v>
+        <v>574</v>
       </c>
       <c r="G2" t="n">
-        <v>653</v>
+        <v>609</v>
       </c>
       <c r="H2" t="n">
-        <v>648</v>
+        <v>590</v>
       </c>
       <c r="I2" t="n">
-        <v>665</v>
+        <v>574</v>
       </c>
       <c r="J2" t="n">
+        <v>537</v>
+      </c>
+      <c r="K2" t="n">
         <v>590</v>
       </c>
-      <c r="K2" t="n">
-        <v>620</v>
-      </c>
       <c r="L2" t="n">
-        <v>643.1</v>
+        <v>598.6</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
+        <v>744</v>
+      </c>
+      <c r="C3" t="n">
+        <v>709</v>
+      </c>
+      <c r="D3" t="n">
+        <v>741</v>
+      </c>
+      <c r="E3" t="n">
+        <v>672</v>
+      </c>
+      <c r="F3" t="n">
+        <v>642</v>
+      </c>
+      <c r="G3" t="n">
+        <v>782</v>
+      </c>
+      <c r="H3" t="n">
         <v>768</v>
       </c>
-      <c r="C3" t="n">
-        <v>848</v>
-      </c>
-      <c r="D3" t="n">
-        <v>794</v>
-      </c>
-      <c r="E3" t="n">
-        <v>836</v>
-      </c>
-      <c r="F3" t="n">
-        <v>770</v>
-      </c>
-      <c r="G3" t="n">
-        <v>744</v>
-      </c>
-      <c r="H3" t="n">
-        <v>769</v>
-      </c>
       <c r="I3" t="n">
-        <v>902</v>
+        <v>837</v>
       </c>
       <c r="J3" t="n">
-        <v>812</v>
+        <v>676</v>
       </c>
       <c r="K3" t="n">
-        <v>781</v>
+        <v>754</v>
       </c>
       <c r="L3" t="n">
-        <v>802.4</v>
+        <v>732.5</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
+        <v>680</v>
+      </c>
+      <c r="C4" t="n">
+        <v>823</v>
+      </c>
+      <c r="D4" t="n">
+        <v>764</v>
+      </c>
+      <c r="E4" t="n">
+        <v>682</v>
+      </c>
+      <c r="F4" t="n">
+        <v>812</v>
+      </c>
+      <c r="G4" t="n">
+        <v>842</v>
+      </c>
+      <c r="H4" t="n">
+        <v>848</v>
+      </c>
+      <c r="I4" t="n">
+        <v>799</v>
+      </c>
+      <c r="J4" t="n">
         <v>723</v>
       </c>
-      <c r="C4" t="n">
-        <v>700</v>
-      </c>
-      <c r="D4" t="n">
-        <v>780</v>
-      </c>
-      <c r="E4" t="n">
-        <v>771</v>
-      </c>
-      <c r="F4" t="n">
-        <v>814</v>
-      </c>
-      <c r="G4" t="n">
-        <v>835</v>
-      </c>
-      <c r="H4" t="n">
-        <v>671</v>
-      </c>
-      <c r="I4" t="n">
-        <v>794</v>
-      </c>
-      <c r="J4" t="n">
-        <v>713</v>
-      </c>
       <c r="K4" t="n">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="L4" t="n">
-        <v>755.9</v>
+        <v>773.5</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>931</v>
+        <v>891</v>
       </c>
       <c r="C5" t="n">
-        <v>867</v>
+        <v>871</v>
       </c>
       <c r="D5" t="n">
-        <v>943</v>
+        <v>772</v>
       </c>
       <c r="E5" t="n">
-        <v>960</v>
+        <v>898</v>
       </c>
       <c r="F5" t="n">
-        <v>923</v>
+        <v>836</v>
       </c>
       <c r="G5" t="n">
-        <v>877</v>
+        <v>870</v>
       </c>
       <c r="H5" t="n">
-        <v>833</v>
+        <v>815</v>
       </c>
       <c r="I5" t="n">
-        <v>941</v>
+        <v>920</v>
       </c>
       <c r="J5" t="n">
-        <v>803</v>
+        <v>933</v>
       </c>
       <c r="K5" t="n">
-        <v>859</v>
+        <v>917</v>
       </c>
       <c r="L5" t="n">
-        <v>893.7</v>
+        <v>872.3</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>706</v>
+        <v>728</v>
       </c>
       <c r="C6" t="n">
+        <v>657</v>
+      </c>
+      <c r="D6" t="n">
+        <v>612</v>
+      </c>
+      <c r="E6" t="n">
+        <v>608</v>
+      </c>
+      <c r="F6" t="n">
+        <v>649</v>
+      </c>
+      <c r="G6" t="n">
         <v>642</v>
       </c>
-      <c r="D6" t="n">
-        <v>648</v>
-      </c>
-      <c r="E6" t="n">
-        <v>677</v>
-      </c>
-      <c r="F6" t="n">
-        <v>706</v>
-      </c>
-      <c r="G6" t="n">
-        <v>600</v>
-      </c>
       <c r="H6" t="n">
-        <v>682</v>
+        <v>597</v>
       </c>
       <c r="I6" t="n">
-        <v>668</v>
+        <v>662</v>
       </c>
       <c r="J6" t="n">
-        <v>632</v>
+        <v>638</v>
       </c>
       <c r="K6" t="n">
-        <v>707</v>
+        <v>664</v>
       </c>
       <c r="L6" t="n">
-        <v>666.8</v>
+        <v>645.7</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>898</v>
+        <v>862</v>
       </c>
       <c r="C7" t="n">
-        <v>794</v>
+        <v>740</v>
       </c>
       <c r="D7" t="n">
-        <v>906</v>
+        <v>789</v>
       </c>
       <c r="E7" t="n">
-        <v>855</v>
+        <v>730</v>
       </c>
       <c r="F7" t="n">
-        <v>779</v>
+        <v>847</v>
       </c>
       <c r="G7" t="n">
-        <v>841</v>
+        <v>766</v>
       </c>
       <c r="H7" t="n">
-        <v>917</v>
+        <v>749</v>
       </c>
       <c r="I7" t="n">
-        <v>844</v>
+        <v>776</v>
       </c>
       <c r="J7" t="n">
-        <v>755</v>
+        <v>735</v>
       </c>
       <c r="K7" t="n">
-        <v>776</v>
+        <v>858</v>
       </c>
       <c r="L7" t="n">
-        <v>836.5</v>
+        <v>785.2</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>646</v>
+        <v>781</v>
       </c>
       <c r="C8" t="n">
-        <v>767</v>
+        <v>678</v>
       </c>
       <c r="D8" t="n">
-        <v>684</v>
+        <v>764</v>
       </c>
       <c r="E8" t="n">
-        <v>646</v>
+        <v>747</v>
       </c>
       <c r="F8" t="n">
-        <v>719</v>
+        <v>644</v>
       </c>
       <c r="G8" t="n">
-        <v>791</v>
+        <v>688</v>
       </c>
       <c r="H8" t="n">
-        <v>696</v>
+        <v>622</v>
       </c>
       <c r="I8" t="n">
-        <v>731</v>
+        <v>742</v>
       </c>
       <c r="J8" t="n">
-        <v>784</v>
+        <v>650</v>
       </c>
       <c r="K8" t="n">
-        <v>741</v>
+        <v>729</v>
       </c>
       <c r="L8" t="n">
-        <v>720.5</v>
+        <v>704.5</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>749</v>
+        <v>628</v>
       </c>
       <c r="C9" t="n">
-        <v>683</v>
+        <v>609</v>
       </c>
       <c r="D9" t="n">
-        <v>658</v>
+        <v>664</v>
       </c>
       <c r="E9" t="n">
-        <v>770</v>
+        <v>681</v>
       </c>
       <c r="F9" t="n">
-        <v>687</v>
+        <v>711</v>
       </c>
       <c r="G9" t="n">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H9" t="n">
-        <v>680</v>
+        <v>634</v>
       </c>
       <c r="I9" t="n">
         <v>632</v>
       </c>
       <c r="J9" t="n">
-        <v>806</v>
+        <v>623</v>
       </c>
       <c r="K9" t="n">
-        <v>737</v>
+        <v>646</v>
       </c>
       <c r="L9" t="n">
-        <v>706</v>
+        <v>648.7</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>850</v>
+        <v>794</v>
       </c>
       <c r="C10" t="n">
-        <v>836</v>
+        <v>736</v>
       </c>
       <c r="D10" t="n">
+        <v>776</v>
+      </c>
+      <c r="E10" t="n">
+        <v>764</v>
+      </c>
+      <c r="F10" t="n">
+        <v>824</v>
+      </c>
+      <c r="G10" t="n">
+        <v>806</v>
+      </c>
+      <c r="H10" t="n">
+        <v>758</v>
+      </c>
+      <c r="I10" t="n">
+        <v>788</v>
+      </c>
+      <c r="J10" t="n">
+        <v>759</v>
+      </c>
+      <c r="K10" t="n">
         <v>749</v>
       </c>
-      <c r="E10" t="n">
-        <v>875</v>
-      </c>
-      <c r="F10" t="n">
-        <v>759</v>
-      </c>
-      <c r="G10" t="n">
-        <v>797</v>
-      </c>
-      <c r="H10" t="n">
-        <v>769</v>
-      </c>
-      <c r="I10" t="n">
-        <v>887</v>
-      </c>
-      <c r="J10" t="n">
-        <v>833</v>
-      </c>
-      <c r="K10" t="n">
-        <v>828</v>
-      </c>
       <c r="L10" t="n">
-        <v>818.3</v>
+        <v>775.4</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>791</v>
+        <v>732</v>
       </c>
       <c r="C11" t="n">
-        <v>826</v>
+        <v>788</v>
       </c>
       <c r="D11" t="n">
-        <v>838</v>
+        <v>755</v>
       </c>
       <c r="E11" t="n">
-        <v>838</v>
+        <v>794</v>
       </c>
       <c r="F11" t="n">
-        <v>848</v>
+        <v>751</v>
       </c>
       <c r="G11" t="n">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="H11" t="n">
-        <v>808</v>
+        <v>765</v>
       </c>
       <c r="I11" t="n">
-        <v>855</v>
+        <v>707</v>
       </c>
       <c r="J11" t="n">
-        <v>782</v>
+        <v>718</v>
       </c>
       <c r="K11" t="n">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="L11" t="n">
-        <v>808.3</v>
+        <v>750.5</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>666</v>
+        <v>718</v>
       </c>
       <c r="C12" t="n">
-        <v>777</v>
+        <v>674</v>
       </c>
       <c r="D12" t="n">
-        <v>714</v>
+        <v>700</v>
       </c>
       <c r="E12" t="n">
-        <v>648</v>
+        <v>685</v>
       </c>
       <c r="F12" t="n">
-        <v>645</v>
+        <v>704</v>
       </c>
       <c r="G12" t="n">
-        <v>737</v>
+        <v>753</v>
       </c>
       <c r="H12" t="n">
-        <v>675</v>
+        <v>713</v>
       </c>
       <c r="I12" t="n">
-        <v>664</v>
+        <v>670</v>
       </c>
       <c r="J12" t="n">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="K12" t="n">
-        <v>692</v>
+        <v>665</v>
       </c>
       <c r="L12" t="n">
-        <v>696.3</v>
+        <v>702.2</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>721</v>
+        <v>651</v>
       </c>
       <c r="C13" t="n">
-        <v>645</v>
+        <v>573</v>
       </c>
       <c r="D13" t="n">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="E13" t="n">
-        <v>832</v>
+        <v>639</v>
       </c>
       <c r="F13" t="n">
-        <v>678</v>
+        <v>581</v>
       </c>
       <c r="G13" t="n">
-        <v>658</v>
+        <v>578</v>
       </c>
       <c r="H13" t="n">
-        <v>721</v>
+        <v>575</v>
       </c>
       <c r="I13" t="n">
-        <v>771</v>
+        <v>590</v>
       </c>
       <c r="J13" t="n">
-        <v>672</v>
+        <v>631</v>
       </c>
       <c r="K13" t="n">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="L13" t="n">
-        <v>687.5</v>
+        <v>599.4</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>663</v>
+        <v>650</v>
       </c>
       <c r="C14" t="n">
-        <v>717</v>
+        <v>646</v>
       </c>
       <c r="D14" t="n">
-        <v>736</v>
+        <v>674</v>
       </c>
       <c r="E14" t="n">
-        <v>739</v>
+        <v>712</v>
       </c>
       <c r="F14" t="n">
-        <v>710</v>
+        <v>675</v>
       </c>
       <c r="G14" t="n">
-        <v>699</v>
+        <v>655</v>
       </c>
       <c r="H14" t="n">
-        <v>732</v>
+        <v>638</v>
       </c>
       <c r="I14" t="n">
-        <v>703</v>
+        <v>737</v>
       </c>
       <c r="J14" t="n">
-        <v>661</v>
+        <v>727</v>
       </c>
       <c r="K14" t="n">
-        <v>669</v>
+        <v>572</v>
       </c>
       <c r="L14" t="n">
-        <v>702.9</v>
+        <v>668.6</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>802</v>
+        <v>739</v>
       </c>
       <c r="C15" t="n">
-        <v>752</v>
+        <v>725</v>
       </c>
       <c r="D15" t="n">
-        <v>715</v>
+        <v>735</v>
       </c>
       <c r="E15" t="n">
-        <v>780</v>
+        <v>727</v>
       </c>
       <c r="F15" t="n">
-        <v>840</v>
+        <v>720</v>
       </c>
       <c r="G15" t="n">
-        <v>720</v>
+        <v>694</v>
       </c>
       <c r="H15" t="n">
-        <v>792</v>
+        <v>739</v>
       </c>
       <c r="I15" t="n">
-        <v>761</v>
+        <v>736</v>
       </c>
       <c r="J15" t="n">
-        <v>811</v>
+        <v>683</v>
       </c>
       <c r="K15" t="n">
-        <v>674</v>
+        <v>735</v>
       </c>
       <c r="L15" t="n">
-        <v>764.7</v>
+        <v>723.3</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>750</v>
+        <v>702</v>
       </c>
       <c r="C16" t="n">
-        <v>811</v>
+        <v>739</v>
       </c>
       <c r="D16" t="n">
-        <v>773</v>
+        <v>725</v>
       </c>
       <c r="E16" t="n">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="F16" t="n">
-        <v>760</v>
+        <v>751</v>
       </c>
       <c r="G16" t="n">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H16" t="n">
-        <v>753</v>
+        <v>722</v>
       </c>
       <c r="I16" t="n">
-        <v>801</v>
+        <v>707</v>
       </c>
       <c r="J16" t="n">
-        <v>679</v>
+        <v>764</v>
       </c>
       <c r="K16" t="n">
-        <v>753</v>
+        <v>780</v>
       </c>
       <c r="L16" t="n">
-        <v>759.6</v>
+        <v>740.5</v>
       </c>
     </row>
     <row r="17">
@@ -1044,34 +1044,34 @@
         <v>910</v>
       </c>
       <c r="C17" t="n">
-        <v>798</v>
+        <v>806</v>
       </c>
       <c r="D17" t="n">
-        <v>764</v>
+        <v>710</v>
       </c>
       <c r="E17" t="n">
-        <v>927</v>
+        <v>752</v>
       </c>
       <c r="F17" t="n">
-        <v>864</v>
+        <v>925</v>
       </c>
       <c r="G17" t="n">
-        <v>817</v>
+        <v>901</v>
       </c>
       <c r="H17" t="n">
-        <v>845</v>
+        <v>791</v>
       </c>
       <c r="I17" t="n">
-        <v>761</v>
+        <v>841</v>
       </c>
       <c r="J17" t="n">
-        <v>827</v>
+        <v>765</v>
       </c>
       <c r="K17" t="n">
-        <v>878</v>
+        <v>894</v>
       </c>
       <c r="L17" t="n">
-        <v>839.1</v>
+        <v>829.5</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>650</v>
+        <v>667</v>
       </c>
       <c r="C18" t="n">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="D18" t="n">
-        <v>685</v>
+        <v>735</v>
       </c>
       <c r="E18" t="n">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="F18" t="n">
-        <v>711</v>
+        <v>682</v>
       </c>
       <c r="G18" t="n">
-        <v>729</v>
+        <v>693</v>
       </c>
       <c r="H18" t="n">
-        <v>704</v>
+        <v>664</v>
       </c>
       <c r="I18" t="n">
-        <v>728</v>
+        <v>640</v>
       </c>
       <c r="J18" t="n">
-        <v>689</v>
+        <v>695</v>
       </c>
       <c r="K18" t="n">
-        <v>731</v>
+        <v>714</v>
       </c>
       <c r="L18" t="n">
-        <v>701.9</v>
+        <v>688.5</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>697</v>
+        <v>794</v>
       </c>
       <c r="C19" t="n">
-        <v>862</v>
+        <v>653</v>
       </c>
       <c r="D19" t="n">
-        <v>840</v>
+        <v>764</v>
       </c>
       <c r="E19" t="n">
-        <v>803</v>
+        <v>781</v>
       </c>
       <c r="F19" t="n">
+        <v>673</v>
+      </c>
+      <c r="G19" t="n">
+        <v>678</v>
+      </c>
+      <c r="H19" t="n">
+        <v>733</v>
+      </c>
+      <c r="I19" t="n">
+        <v>708</v>
+      </c>
+      <c r="J19" t="n">
         <v>762</v>
       </c>
-      <c r="G19" t="n">
-        <v>765</v>
-      </c>
-      <c r="H19" t="n">
-        <v>807</v>
-      </c>
-      <c r="I19" t="n">
-        <v>715</v>
-      </c>
-      <c r="J19" t="n">
-        <v>693</v>
-      </c>
       <c r="K19" t="n">
-        <v>765</v>
+        <v>744</v>
       </c>
       <c r="L19" t="n">
-        <v>770.9</v>
+        <v>729</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
+        <v>721</v>
+      </c>
+      <c r="C20" t="n">
+        <v>820</v>
+      </c>
+      <c r="D20" t="n">
+        <v>687</v>
+      </c>
+      <c r="E20" t="n">
+        <v>674</v>
+      </c>
+      <c r="F20" t="n">
         <v>724</v>
       </c>
-      <c r="C20" t="n">
-        <v>741</v>
-      </c>
-      <c r="D20" t="n">
-        <v>798</v>
-      </c>
-      <c r="E20" t="n">
-        <v>713</v>
-      </c>
-      <c r="F20" t="n">
-        <v>679</v>
-      </c>
       <c r="G20" t="n">
-        <v>786</v>
+        <v>635</v>
       </c>
       <c r="H20" t="n">
-        <v>784</v>
+        <v>704</v>
       </c>
       <c r="I20" t="n">
-        <v>760</v>
+        <v>700</v>
       </c>
       <c r="J20" t="n">
-        <v>788</v>
+        <v>708</v>
       </c>
       <c r="K20" t="n">
-        <v>720</v>
+        <v>750</v>
       </c>
       <c r="L20" t="n">
-        <v>749.3</v>
+        <v>712.3</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>758</v>
+        <v>676</v>
       </c>
       <c r="C21" t="n">
-        <v>692</v>
+        <v>769</v>
       </c>
       <c r="D21" t="n">
-        <v>685</v>
+        <v>751</v>
       </c>
       <c r="E21" t="n">
-        <v>773</v>
+        <v>658</v>
       </c>
       <c r="F21" t="n">
-        <v>775</v>
+        <v>710</v>
       </c>
       <c r="G21" t="n">
-        <v>685</v>
+        <v>722</v>
       </c>
       <c r="H21" t="n">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="I21" t="n">
-        <v>728</v>
+        <v>690</v>
       </c>
       <c r="J21" t="n">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="K21" t="n">
-        <v>652</v>
+        <v>746</v>
       </c>
       <c r="L21" t="n">
-        <v>708.2</v>
+        <v>705.1</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>675</v>
+        <v>642</v>
       </c>
       <c r="C22" t="n">
-        <v>681</v>
+        <v>640</v>
       </c>
       <c r="D22" t="n">
-        <v>657</v>
+        <v>619</v>
       </c>
       <c r="E22" t="n">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="F22" t="n">
-        <v>665</v>
+        <v>604</v>
       </c>
       <c r="G22" t="n">
-        <v>636</v>
+        <v>485</v>
       </c>
       <c r="H22" t="n">
-        <v>655</v>
+        <v>621</v>
       </c>
       <c r="I22" t="n">
-        <v>697</v>
+        <v>612</v>
       </c>
       <c r="J22" t="n">
-        <v>701</v>
+        <v>640</v>
       </c>
       <c r="K22" t="n">
-        <v>686</v>
+        <v>558</v>
       </c>
       <c r="L22" t="n">
-        <v>667</v>
+        <v>604.4</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>813</v>
+        <v>732</v>
       </c>
       <c r="C23" t="n">
-        <v>872</v>
+        <v>776</v>
       </c>
       <c r="D23" t="n">
-        <v>782</v>
+        <v>672</v>
       </c>
       <c r="E23" t="n">
-        <v>716</v>
+        <v>669</v>
       </c>
       <c r="F23" t="n">
-        <v>865</v>
+        <v>661</v>
       </c>
       <c r="G23" t="n">
-        <v>747</v>
+        <v>764</v>
       </c>
       <c r="H23" t="n">
+        <v>780</v>
+      </c>
+      <c r="I23" t="n">
+        <v>718</v>
+      </c>
+      <c r="J23" t="n">
+        <v>834</v>
+      </c>
+      <c r="K23" t="n">
         <v>708</v>
       </c>
-      <c r="I23" t="n">
-        <v>707</v>
-      </c>
-      <c r="J23" t="n">
-        <v>775</v>
-      </c>
-      <c r="K23" t="n">
-        <v>751</v>
-      </c>
       <c r="L23" t="n">
-        <v>773.6</v>
+        <v>731.4</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>660</v>
+        <v>685</v>
       </c>
       <c r="C24" t="n">
-        <v>733</v>
+        <v>668</v>
       </c>
       <c r="D24" t="n">
-        <v>690</v>
+        <v>799</v>
       </c>
       <c r="E24" t="n">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="F24" t="n">
-        <v>721</v>
+        <v>672</v>
       </c>
       <c r="G24" t="n">
-        <v>657</v>
+        <v>688</v>
       </c>
       <c r="H24" t="n">
         <v>753</v>
       </c>
       <c r="I24" t="n">
-        <v>801</v>
+        <v>743</v>
       </c>
       <c r="J24" t="n">
-        <v>770</v>
+        <v>665</v>
       </c>
       <c r="K24" t="n">
-        <v>683</v>
+        <v>774</v>
       </c>
       <c r="L24" t="n">
-        <v>721</v>
+        <v>718.4</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>817</v>
+        <v>659</v>
       </c>
       <c r="C25" t="n">
-        <v>753</v>
+        <v>647</v>
       </c>
       <c r="D25" t="n">
-        <v>716</v>
+        <v>622</v>
       </c>
       <c r="E25" t="n">
-        <v>720</v>
+        <v>637</v>
       </c>
       <c r="F25" t="n">
-        <v>773</v>
+        <v>665</v>
       </c>
       <c r="G25" t="n">
-        <v>798</v>
+        <v>669</v>
       </c>
       <c r="H25" t="n">
-        <v>823</v>
+        <v>630</v>
       </c>
       <c r="I25" t="n">
-        <v>783</v>
+        <v>636</v>
       </c>
       <c r="J25" t="n">
-        <v>691</v>
+        <v>707</v>
       </c>
       <c r="K25" t="n">
-        <v>650</v>
+        <v>730</v>
       </c>
       <c r="L25" t="n">
-        <v>752.4</v>
+        <v>660.2</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>757</v>
+        <v>708</v>
       </c>
       <c r="C26" t="n">
-        <v>763</v>
+        <v>743</v>
       </c>
       <c r="D26" t="n">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="E26" t="n">
-        <v>728</v>
+        <v>755</v>
       </c>
       <c r="F26" t="n">
-        <v>800</v>
+        <v>707</v>
       </c>
       <c r="G26" t="n">
-        <v>708</v>
+        <v>779</v>
       </c>
       <c r="H26" t="n">
-        <v>696</v>
+        <v>727</v>
       </c>
       <c r="I26" t="n">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="J26" t="n">
-        <v>788</v>
+        <v>722</v>
       </c>
       <c r="K26" t="n">
-        <v>733</v>
+        <v>750</v>
       </c>
       <c r="L26" t="n">
-        <v>753</v>
+        <v>744.2</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>918</v>
+        <v>770</v>
       </c>
       <c r="C27" t="n">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="D27" t="n">
-        <v>803</v>
+        <v>832</v>
       </c>
       <c r="E27" t="n">
-        <v>740</v>
+        <v>781</v>
       </c>
       <c r="F27" t="n">
-        <v>805</v>
+        <v>700</v>
       </c>
       <c r="G27" t="n">
-        <v>839</v>
+        <v>804</v>
       </c>
       <c r="H27" t="n">
-        <v>787</v>
+        <v>752</v>
       </c>
       <c r="I27" t="n">
-        <v>780</v>
+        <v>738</v>
       </c>
       <c r="J27" t="n">
-        <v>869</v>
+        <v>798</v>
       </c>
       <c r="K27" t="n">
-        <v>719</v>
+        <v>880</v>
       </c>
       <c r="L27" t="n">
-        <v>802.6</v>
+        <v>782.5</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>730</v>
+        <v>613</v>
       </c>
       <c r="C28" t="n">
-        <v>736</v>
+        <v>654</v>
       </c>
       <c r="D28" t="n">
-        <v>726</v>
+        <v>605</v>
       </c>
       <c r="E28" t="n">
-        <v>667</v>
+        <v>638</v>
       </c>
       <c r="F28" t="n">
-        <v>695</v>
+        <v>658</v>
       </c>
       <c r="G28" t="n">
-        <v>691</v>
+        <v>608</v>
       </c>
       <c r="H28" t="n">
-        <v>701</v>
+        <v>625</v>
       </c>
       <c r="I28" t="n">
-        <v>637</v>
+        <v>665</v>
       </c>
       <c r="J28" t="n">
-        <v>651</v>
+        <v>687</v>
       </c>
       <c r="K28" t="n">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="L28" t="n">
-        <v>689.1</v>
+        <v>640.5</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>808</v>
+        <v>837</v>
       </c>
       <c r="C29" t="n">
-        <v>832</v>
+        <v>689</v>
       </c>
       <c r="D29" t="n">
-        <v>716</v>
+        <v>735</v>
       </c>
       <c r="E29" t="n">
-        <v>814</v>
+        <v>773</v>
       </c>
       <c r="F29" t="n">
-        <v>795</v>
+        <v>774</v>
       </c>
       <c r="G29" t="n">
-        <v>722</v>
+        <v>708</v>
       </c>
       <c r="H29" t="n">
-        <v>772</v>
+        <v>644</v>
       </c>
       <c r="I29" t="n">
-        <v>858</v>
+        <v>704</v>
       </c>
       <c r="J29" t="n">
-        <v>753</v>
+        <v>688</v>
       </c>
       <c r="K29" t="n">
-        <v>805</v>
+        <v>719</v>
       </c>
       <c r="L29" t="n">
-        <v>787.5</v>
+        <v>727.1</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C30" t="n">
-        <v>912</v>
+        <v>679</v>
       </c>
       <c r="D30" t="n">
-        <v>813</v>
+        <v>723</v>
       </c>
       <c r="E30" t="n">
-        <v>725</v>
+        <v>671</v>
       </c>
       <c r="F30" t="n">
-        <v>773</v>
+        <v>654</v>
       </c>
       <c r="G30" t="n">
-        <v>732</v>
+        <v>659</v>
       </c>
       <c r="H30" t="n">
-        <v>800</v>
+        <v>779</v>
       </c>
       <c r="I30" t="n">
-        <v>816</v>
+        <v>749</v>
       </c>
       <c r="J30" t="n">
-        <v>671</v>
+        <v>781</v>
       </c>
       <c r="K30" t="n">
-        <v>824</v>
+        <v>739</v>
       </c>
       <c r="L30" t="n">
-        <v>786.1</v>
+        <v>722.7</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>718</v>
+        <v>755</v>
       </c>
       <c r="C31" t="n">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D31" t="n">
-        <v>670</v>
+        <v>777</v>
       </c>
       <c r="E31" t="n">
-        <v>771</v>
+        <v>705</v>
       </c>
       <c r="F31" t="n">
-        <v>815</v>
+        <v>706</v>
       </c>
       <c r="G31" t="n">
-        <v>746</v>
+        <v>761</v>
       </c>
       <c r="H31" t="n">
-        <v>714</v>
+        <v>804</v>
       </c>
       <c r="I31" t="n">
-        <v>653</v>
+        <v>765</v>
       </c>
       <c r="J31" t="n">
-        <v>745</v>
+        <v>706</v>
       </c>
       <c r="K31" t="n">
-        <v>677</v>
+        <v>782</v>
       </c>
       <c r="L31" t="n">
-        <v>725.8</v>
+        <v>751.1</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>737</v>
+        <v>662</v>
       </c>
       <c r="C32" t="n">
-        <v>711</v>
+        <v>681</v>
       </c>
       <c r="D32" t="n">
-        <v>761</v>
+        <v>634</v>
       </c>
       <c r="E32" t="n">
-        <v>748</v>
+        <v>680</v>
       </c>
       <c r="F32" t="n">
-        <v>703</v>
+        <v>651</v>
       </c>
       <c r="G32" t="n">
-        <v>610</v>
+        <v>686</v>
       </c>
       <c r="H32" t="n">
-        <v>693</v>
+        <v>637</v>
       </c>
       <c r="I32" t="n">
-        <v>658</v>
+        <v>605</v>
       </c>
       <c r="J32" t="n">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="K32" t="n">
-        <v>648</v>
+        <v>626</v>
       </c>
       <c r="L32" t="n">
-        <v>694.8</v>
+        <v>654.3</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>911</v>
+        <v>804</v>
       </c>
       <c r="C33" t="n">
-        <v>712</v>
+        <v>759</v>
       </c>
       <c r="D33" t="n">
-        <v>757</v>
+        <v>829</v>
       </c>
       <c r="E33" t="n">
-        <v>795</v>
+        <v>809</v>
       </c>
       <c r="F33" t="n">
-        <v>932</v>
+        <v>724</v>
       </c>
       <c r="G33" t="n">
-        <v>791</v>
+        <v>695</v>
       </c>
       <c r="H33" t="n">
-        <v>806</v>
+        <v>833</v>
       </c>
       <c r="I33" t="n">
-        <v>733</v>
+        <v>761</v>
       </c>
       <c r="J33" t="n">
-        <v>733</v>
+        <v>789</v>
       </c>
       <c r="K33" t="n">
-        <v>798</v>
+        <v>781</v>
       </c>
       <c r="L33" t="n">
-        <v>796.8</v>
+        <v>778.4</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>726</v>
+        <v>668</v>
       </c>
       <c r="C34" t="n">
-        <v>764</v>
+        <v>684</v>
       </c>
       <c r="D34" t="n">
-        <v>607</v>
+        <v>736</v>
       </c>
       <c r="E34" t="n">
-        <v>771</v>
+        <v>692</v>
       </c>
       <c r="F34" t="n">
-        <v>732</v>
+        <v>692</v>
       </c>
       <c r="G34" t="n">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="H34" t="n">
-        <v>834</v>
+        <v>668</v>
       </c>
       <c r="I34" t="n">
-        <v>682</v>
+        <v>714</v>
       </c>
       <c r="J34" t="n">
-        <v>742</v>
+        <v>648</v>
       </c>
       <c r="K34" t="n">
-        <v>709</v>
+        <v>691</v>
       </c>
       <c r="L34" t="n">
-        <v>721.8</v>
+        <v>683.8</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>730</v>
+        <v>773</v>
       </c>
       <c r="C35" t="n">
-        <v>830</v>
+        <v>814</v>
       </c>
       <c r="D35" t="n">
-        <v>787</v>
+        <v>771</v>
       </c>
       <c r="E35" t="n">
-        <v>722</v>
+        <v>737</v>
       </c>
       <c r="F35" t="n">
-        <v>874</v>
+        <v>709</v>
       </c>
       <c r="G35" t="n">
-        <v>794</v>
+        <v>759</v>
       </c>
       <c r="H35" t="n">
-        <v>855</v>
+        <v>784</v>
       </c>
       <c r="I35" t="n">
-        <v>856</v>
+        <v>766</v>
       </c>
       <c r="J35" t="n">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="K35" t="n">
-        <v>814</v>
+        <v>788</v>
       </c>
       <c r="L35" t="n">
-        <v>810.7</v>
+        <v>774.8</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>752</v>
+        <v>602</v>
       </c>
       <c r="C36" t="n">
-        <v>641</v>
+        <v>660</v>
       </c>
       <c r="D36" t="n">
-        <v>640</v>
+        <v>618</v>
       </c>
       <c r="E36" t="n">
-        <v>685</v>
+        <v>694</v>
       </c>
       <c r="F36" t="n">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="G36" t="n">
-        <v>711</v>
+        <v>584</v>
       </c>
       <c r="H36" t="n">
-        <v>637</v>
+        <v>594</v>
       </c>
       <c r="I36" t="n">
-        <v>706</v>
+        <v>608</v>
       </c>
       <c r="J36" t="n">
-        <v>650</v>
+        <v>594</v>
       </c>
       <c r="K36" t="n">
-        <v>696</v>
+        <v>594</v>
       </c>
       <c r="L36" t="n">
-        <v>671.7</v>
+        <v>614.2</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>708</v>
+        <v>678</v>
       </c>
       <c r="C37" t="n">
-        <v>774</v>
+        <v>704</v>
       </c>
       <c r="D37" t="n">
-        <v>808</v>
+        <v>734</v>
       </c>
       <c r="E37" t="n">
-        <v>707</v>
+        <v>701</v>
       </c>
       <c r="F37" t="n">
-        <v>780</v>
+        <v>752</v>
       </c>
       <c r="G37" t="n">
-        <v>773</v>
+        <v>678</v>
       </c>
       <c r="H37" t="n">
-        <v>871</v>
+        <v>675</v>
       </c>
       <c r="I37" t="n">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="J37" t="n">
-        <v>918</v>
+        <v>685</v>
       </c>
       <c r="K37" t="n">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="L37" t="n">
-        <v>779</v>
+        <v>706.2</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>695</v>
+        <v>729</v>
       </c>
       <c r="C38" t="n">
-        <v>757</v>
+        <v>673</v>
       </c>
       <c r="D38" t="n">
-        <v>807</v>
+        <v>748</v>
       </c>
       <c r="E38" t="n">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="F38" t="n">
-        <v>836</v>
+        <v>733</v>
       </c>
       <c r="G38" t="n">
-        <v>802</v>
+        <v>756</v>
       </c>
       <c r="H38" t="n">
-        <v>776</v>
+        <v>711</v>
       </c>
       <c r="I38" t="n">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="J38" t="n">
-        <v>777</v>
+        <v>683</v>
       </c>
       <c r="K38" t="n">
-        <v>808</v>
+        <v>742</v>
       </c>
       <c r="L38" t="n">
-        <v>778.4</v>
+        <v>730</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>656</v>
+        <v>552</v>
       </c>
       <c r="C39" t="n">
-        <v>631</v>
+        <v>618</v>
       </c>
       <c r="D39" t="n">
-        <v>664</v>
+        <v>620</v>
       </c>
       <c r="E39" t="n">
-        <v>614</v>
+        <v>560</v>
       </c>
       <c r="F39" t="n">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="G39" t="n">
-        <v>706</v>
+        <v>620</v>
       </c>
       <c r="H39" t="n">
-        <v>676</v>
+        <v>580</v>
       </c>
       <c r="I39" t="n">
-        <v>611</v>
+        <v>554</v>
       </c>
       <c r="J39" t="n">
-        <v>607</v>
+        <v>594</v>
       </c>
       <c r="K39" t="n">
-        <v>596</v>
+        <v>663</v>
       </c>
       <c r="L39" t="n">
-        <v>642.9</v>
+        <v>602.1</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>761</v>
+        <v>824</v>
       </c>
       <c r="C40" t="n">
-        <v>762</v>
+        <v>852</v>
       </c>
       <c r="D40" t="n">
-        <v>947</v>
+        <v>858</v>
       </c>
       <c r="E40" t="n">
-        <v>808</v>
+        <v>775</v>
       </c>
       <c r="F40" t="n">
-        <v>780</v>
+        <v>792</v>
       </c>
       <c r="G40" t="n">
-        <v>768</v>
+        <v>821</v>
       </c>
       <c r="H40" t="n">
-        <v>809</v>
+        <v>795</v>
       </c>
       <c r="I40" t="n">
-        <v>690</v>
+        <v>790</v>
       </c>
       <c r="J40" t="n">
-        <v>770</v>
+        <v>841</v>
       </c>
       <c r="K40" t="n">
-        <v>694</v>
+        <v>733</v>
       </c>
       <c r="L40" t="n">
-        <v>778.9</v>
+        <v>808.1</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>678</v>
+        <v>638</v>
       </c>
       <c r="C41" t="n">
-        <v>728</v>
+        <v>632</v>
       </c>
       <c r="D41" t="n">
-        <v>761</v>
+        <v>566</v>
       </c>
       <c r="E41" t="n">
-        <v>782</v>
+        <v>590</v>
       </c>
       <c r="F41" t="n">
-        <v>762</v>
+        <v>626</v>
       </c>
       <c r="G41" t="n">
-        <v>660</v>
+        <v>570</v>
       </c>
       <c r="H41" t="n">
-        <v>634</v>
+        <v>654</v>
       </c>
       <c r="I41" t="n">
-        <v>736</v>
+        <v>629</v>
       </c>
       <c r="J41" t="n">
-        <v>798</v>
+        <v>646</v>
       </c>
       <c r="K41" t="n">
-        <v>634</v>
+        <v>618</v>
       </c>
       <c r="L41" t="n">
-        <v>717.3</v>
+        <v>616.9</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>837</v>
+        <v>617</v>
       </c>
       <c r="C42" t="n">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="D42" t="n">
-        <v>659</v>
+        <v>621</v>
       </c>
       <c r="E42" t="n">
-        <v>652</v>
+        <v>562</v>
       </c>
       <c r="F42" t="n">
-        <v>687</v>
+        <v>653</v>
       </c>
       <c r="G42" t="n">
-        <v>599</v>
+        <v>705</v>
       </c>
       <c r="H42" t="n">
-        <v>689</v>
+        <v>614</v>
       </c>
       <c r="I42" t="n">
-        <v>698</v>
+        <v>684</v>
       </c>
       <c r="J42" t="n">
-        <v>693</v>
+        <v>666</v>
       </c>
       <c r="K42" t="n">
-        <v>685</v>
+        <v>638</v>
       </c>
       <c r="L42" t="n">
-        <v>690.5</v>
+        <v>646.3</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="C43" t="n">
-        <v>921</v>
+        <v>798</v>
       </c>
       <c r="D43" t="n">
-        <v>708</v>
+        <v>770</v>
       </c>
       <c r="E43" t="n">
-        <v>710</v>
+        <v>861</v>
       </c>
       <c r="F43" t="n">
-        <v>772</v>
+        <v>712</v>
       </c>
       <c r="G43" t="n">
-        <v>782</v>
+        <v>717</v>
       </c>
       <c r="H43" t="n">
-        <v>779</v>
+        <v>720</v>
       </c>
       <c r="I43" t="n">
-        <v>764</v>
+        <v>685</v>
       </c>
       <c r="J43" t="n">
-        <v>701</v>
+        <v>766</v>
       </c>
       <c r="K43" t="n">
-        <v>832</v>
+        <v>790</v>
       </c>
       <c r="L43" t="n">
-        <v>771.3</v>
+        <v>756.7</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="C44" t="n">
-        <v>655</v>
+        <v>788</v>
       </c>
       <c r="D44" t="n">
-        <v>829</v>
+        <v>706</v>
       </c>
       <c r="E44" t="n">
-        <v>725</v>
+        <v>788</v>
       </c>
       <c r="F44" t="n">
-        <v>865</v>
+        <v>763</v>
       </c>
       <c r="G44" t="n">
-        <v>821</v>
+        <v>852</v>
       </c>
       <c r="H44" t="n">
-        <v>788</v>
+        <v>748</v>
       </c>
       <c r="I44" t="n">
-        <v>693</v>
+        <v>808</v>
       </c>
       <c r="J44" t="n">
-        <v>852</v>
+        <v>832</v>
       </c>
       <c r="K44" t="n">
-        <v>832</v>
+        <v>696</v>
       </c>
       <c r="L44" t="n">
-        <v>781</v>
+        <v>772.8</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C45" t="n">
-        <v>679</v>
+        <v>613</v>
       </c>
       <c r="D45" t="n">
-        <v>676</v>
+        <v>625</v>
       </c>
       <c r="E45" t="n">
-        <v>710</v>
+        <v>573</v>
       </c>
       <c r="F45" t="n">
-        <v>654</v>
+        <v>594</v>
       </c>
       <c r="G45" t="n">
-        <v>682</v>
+        <v>605</v>
       </c>
       <c r="H45" t="n">
-        <v>679</v>
+        <v>587</v>
       </c>
       <c r="I45" t="n">
-        <v>711</v>
+        <v>565</v>
       </c>
       <c r="J45" t="n">
-        <v>650</v>
+        <v>563</v>
       </c>
       <c r="K45" t="n">
-        <v>620</v>
+        <v>608</v>
       </c>
       <c r="L45" t="n">
-        <v>668.8</v>
+        <v>596.1</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>615</v>
+        <v>702</v>
       </c>
       <c r="C46" t="n">
-        <v>736</v>
+        <v>694</v>
       </c>
       <c r="D46" t="n">
-        <v>701</v>
+        <v>685</v>
       </c>
       <c r="E46" t="n">
-        <v>690</v>
+        <v>614</v>
       </c>
       <c r="F46" t="n">
-        <v>716</v>
+        <v>624</v>
       </c>
       <c r="G46" t="n">
-        <v>708</v>
+        <v>676</v>
       </c>
       <c r="H46" t="n">
-        <v>686</v>
+        <v>622</v>
       </c>
       <c r="I46" t="n">
-        <v>629</v>
+        <v>634</v>
       </c>
       <c r="J46" t="n">
-        <v>790</v>
+        <v>700</v>
       </c>
       <c r="K46" t="n">
-        <v>672</v>
+        <v>706</v>
       </c>
       <c r="L46" t="n">
-        <v>694.3</v>
+        <v>665.7</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>813</v>
+        <v>791</v>
       </c>
       <c r="C47" t="n">
-        <v>778</v>
+        <v>739</v>
       </c>
       <c r="D47" t="n">
-        <v>785</v>
+        <v>766</v>
       </c>
       <c r="E47" t="n">
-        <v>827</v>
+        <v>753</v>
       </c>
       <c r="F47" t="n">
-        <v>776</v>
+        <v>720</v>
       </c>
       <c r="G47" t="n">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="H47" t="n">
-        <v>859</v>
+        <v>795</v>
       </c>
       <c r="I47" t="n">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="J47" t="n">
-        <v>845</v>
+        <v>766</v>
       </c>
       <c r="K47" t="n">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="L47" t="n">
-        <v>791.7</v>
+        <v>755</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>724</v>
+        <v>689</v>
       </c>
       <c r="C48" t="n">
+        <v>583</v>
+      </c>
+      <c r="D48" t="n">
+        <v>717</v>
+      </c>
+      <c r="E48" t="n">
+        <v>583</v>
+      </c>
+      <c r="F48" t="n">
         <v>701</v>
       </c>
-      <c r="D48" t="n">
-        <v>763</v>
-      </c>
-      <c r="E48" t="n">
-        <v>854</v>
-      </c>
-      <c r="F48" t="n">
-        <v>674</v>
-      </c>
       <c r="G48" t="n">
-        <v>778</v>
+        <v>698</v>
       </c>
       <c r="H48" t="n">
-        <v>725</v>
+        <v>664</v>
       </c>
       <c r="I48" t="n">
-        <v>614</v>
+        <v>567</v>
       </c>
       <c r="J48" t="n">
-        <v>627</v>
+        <v>739</v>
       </c>
       <c r="K48" t="n">
-        <v>757</v>
+        <v>650</v>
       </c>
       <c r="L48" t="n">
-        <v>721.7</v>
+        <v>659.1</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>856</v>
+        <v>829</v>
       </c>
       <c r="C49" t="n">
-        <v>790</v>
+        <v>780</v>
       </c>
       <c r="D49" t="n">
-        <v>831</v>
+        <v>818</v>
       </c>
       <c r="E49" t="n">
-        <v>770</v>
+        <v>784</v>
       </c>
       <c r="F49" t="n">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="G49" t="n">
-        <v>827</v>
+        <v>816</v>
       </c>
       <c r="H49" t="n">
-        <v>835</v>
+        <v>894</v>
       </c>
       <c r="I49" t="n">
-        <v>795</v>
+        <v>837</v>
       </c>
       <c r="J49" t="n">
-        <v>805</v>
+        <v>884</v>
       </c>
       <c r="K49" t="n">
-        <v>884</v>
+        <v>824</v>
       </c>
       <c r="L49" t="n">
-        <v>822</v>
+        <v>829.6</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="C50" t="n">
-        <v>672</v>
+        <v>705</v>
       </c>
       <c r="D50" t="n">
-        <v>661</v>
+        <v>671</v>
       </c>
       <c r="E50" t="n">
-        <v>767</v>
+        <v>705</v>
       </c>
       <c r="F50" t="n">
-        <v>730</v>
+        <v>640</v>
       </c>
       <c r="G50" t="n">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="H50" t="n">
-        <v>702</v>
+        <v>658</v>
       </c>
       <c r="I50" t="n">
-        <v>720</v>
+        <v>680</v>
       </c>
       <c r="J50" t="n">
-        <v>598</v>
+        <v>623</v>
       </c>
       <c r="K50" t="n">
-        <v>689</v>
+        <v>660</v>
       </c>
       <c r="L50" t="n">
-        <v>692.4</v>
+        <v>672.5</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>714</v>
+        <v>725</v>
       </c>
       <c r="C51" t="n">
-        <v>809</v>
+        <v>683</v>
       </c>
       <c r="D51" t="n">
-        <v>765</v>
+        <v>752</v>
       </c>
       <c r="E51" t="n">
-        <v>772</v>
+        <v>687</v>
       </c>
       <c r="F51" t="n">
-        <v>772</v>
+        <v>736</v>
       </c>
       <c r="G51" t="n">
         <v>745</v>
       </c>
       <c r="H51" t="n">
-        <v>721</v>
+        <v>688</v>
       </c>
       <c r="I51" t="n">
-        <v>718</v>
+        <v>732</v>
       </c>
       <c r="J51" t="n">
-        <v>708</v>
+        <v>647</v>
       </c>
       <c r="K51" t="n">
-        <v>645</v>
+        <v>705</v>
       </c>
       <c r="L51" t="n">
-        <v>736.9</v>
+        <v>710</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>748.96</v>
+        <v>720.52</v>
       </c>
       <c r="C52" t="n">
-        <v>751.98</v>
+        <v>709.28</v>
       </c>
       <c r="D52" t="n">
-        <v>744.62</v>
+        <v>716.36</v>
       </c>
       <c r="E52" t="n">
-        <v>755.26</v>
+        <v>703.62</v>
       </c>
       <c r="F52" t="n">
-        <v>758.9400000000001</v>
+        <v>702.84</v>
       </c>
       <c r="G52" t="n">
-        <v>737.36</v>
+        <v>710.02</v>
       </c>
       <c r="H52" t="n">
-        <v>748.26</v>
+        <v>702.38</v>
       </c>
       <c r="I52" t="n">
-        <v>740.0599999999999</v>
+        <v>706.72</v>
       </c>
       <c r="J52" t="n">
-        <v>738.9400000000001</v>
+        <v>711.2</v>
       </c>
       <c r="K52" t="n">
-        <v>726.2</v>
+        <v>717.14</v>
       </c>
       <c r="L52" t="n">
-        <v>745.0580000000002</v>
+        <v>710.008</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4.680085182189941</v>
+        <v>4.14890456199646</v>
       </c>
       <c r="C2" t="n">
-        <v>3.818870067596436</v>
+        <v>4.333409547805786</v>
       </c>
       <c r="D2" t="n">
-        <v>4.359585523605347</v>
+        <v>4.63959264755249</v>
       </c>
       <c r="E2" t="n">
-        <v>4.490015506744385</v>
+        <v>4.124969005584717</v>
       </c>
       <c r="F2" t="n">
-        <v>5.916089296340942</v>
+        <v>4.656546831130981</v>
       </c>
       <c r="G2" t="n">
-        <v>4.948006868362427</v>
+        <v>4.10591721534729</v>
       </c>
       <c r="H2" t="n">
-        <v>4.648426532745361</v>
+        <v>4.17284083366394</v>
       </c>
       <c r="I2" t="n">
-        <v>4.641381978988647</v>
+        <v>4.641587495803833</v>
       </c>
       <c r="J2" t="n">
-        <v>4.41232442855835</v>
+        <v>4.112003803253174</v>
       </c>
       <c r="K2" t="n">
-        <v>4.803043603897095</v>
+        <v>4.099037885665894</v>
       </c>
       <c r="L2" t="n">
-        <v>4.671782898902893</v>
+        <v>4.303480982780457</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>5.542647361755371</v>
+        <v>4.99065375328064</v>
       </c>
       <c r="C3" t="n">
-        <v>4.838455200195312</v>
+        <v>4.561814785003662</v>
       </c>
       <c r="D3" t="n">
-        <v>5.803643226623535</v>
+        <v>5.099363327026367</v>
       </c>
       <c r="E3" t="n">
-        <v>5.877257585525513</v>
+        <v>4.447107076644897</v>
       </c>
       <c r="F3" t="n">
-        <v>4.534736156463623</v>
+        <v>4.280553340911865</v>
       </c>
       <c r="G3" t="n">
-        <v>5.769843816757202</v>
+        <v>4.483067750930786</v>
       </c>
       <c r="H3" t="n">
-        <v>4.703447341918945</v>
+        <v>4.505950450897217</v>
       </c>
       <c r="I3" t="n">
-        <v>5.635607957839966</v>
+        <v>4.723369359970093</v>
       </c>
       <c r="J3" t="n">
-        <v>5.809709310531616</v>
+        <v>4.814126014709473</v>
       </c>
       <c r="K3" t="n">
-        <v>4.447951555252075</v>
+        <v>4.944776773452759</v>
       </c>
       <c r="L3" t="n">
-        <v>5.296329951286316</v>
+        <v>4.685078263282776</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>4.935291767120361</v>
+        <v>5.324756622314453</v>
       </c>
       <c r="C4" t="n">
-        <v>5.652547121047974</v>
+        <v>5.21405553817749</v>
       </c>
       <c r="D4" t="n">
-        <v>5.372753620147705</v>
+        <v>4.809998273849487</v>
       </c>
       <c r="E4" t="n">
-        <v>5.314006805419922</v>
+        <v>4.40273642539978</v>
       </c>
       <c r="F4" t="n">
-        <v>5.575038433074951</v>
+        <v>5.021570920944214</v>
       </c>
       <c r="G4" t="n">
-        <v>4.801206111907959</v>
+        <v>4.620643854141235</v>
       </c>
       <c r="H4" t="n">
-        <v>5.311275005340576</v>
+        <v>5.27988076210022</v>
       </c>
       <c r="I4" t="n">
-        <v>6.176099300384521</v>
+        <v>4.642584562301636</v>
       </c>
       <c r="J4" t="n">
-        <v>5.753694295883179</v>
+        <v>4.839059829711914</v>
       </c>
       <c r="K4" t="n">
-        <v>6.907846450805664</v>
+        <v>4.900083541870117</v>
       </c>
       <c r="L4" t="n">
-        <v>5.579975891113281</v>
+        <v>4.905537033081055</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>5.538502931594849</v>
+        <v>5.592045545578003</v>
       </c>
       <c r="C5" t="n">
-        <v>5.492161989212036</v>
+        <v>5.729677438735962</v>
       </c>
       <c r="D5" t="n">
-        <v>5.445961713790894</v>
+        <v>4.748302221298218</v>
       </c>
       <c r="E5" t="n">
-        <v>5.652284145355225</v>
+        <v>5.713719844818115</v>
       </c>
       <c r="F5" t="n">
-        <v>5.274291038513184</v>
+        <v>4.89989709854126</v>
       </c>
       <c r="G5" t="n">
-        <v>5.929308176040649</v>
+        <v>5.531967401504517</v>
       </c>
       <c r="H5" t="n">
-        <v>5.231775999069214</v>
+        <v>5.00361967086792</v>
       </c>
       <c r="I5" t="n">
-        <v>5.625268936157227</v>
+        <v>5.161197900772095</v>
       </c>
       <c r="J5" t="n">
-        <v>5.468096733093262</v>
+        <v>5.467378616333008</v>
       </c>
       <c r="K5" t="n">
-        <v>5.427029132843018</v>
+        <v>5.090599775314331</v>
       </c>
       <c r="L5" t="n">
-        <v>5.508468079566955</v>
+        <v>5.293840551376343</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>4.625278234481812</v>
+        <v>4.00136661529541</v>
       </c>
       <c r="C6" t="n">
-        <v>3.796889066696167</v>
+        <v>4.134185075759888</v>
       </c>
       <c r="D6" t="n">
-        <v>4.30979061126709</v>
+        <v>3.845715522766113</v>
       </c>
       <c r="E6" t="n">
-        <v>3.623527526855469</v>
+        <v>4.118984460830688</v>
       </c>
       <c r="F6" t="n">
-        <v>4.155770063400269</v>
+        <v>3.997310638427734</v>
       </c>
       <c r="G6" t="n">
-        <v>3.647591352462769</v>
+        <v>3.937365293502808</v>
       </c>
       <c r="H6" t="n">
-        <v>3.724661350250244</v>
+        <v>3.902564287185669</v>
       </c>
       <c r="I6" t="n">
-        <v>3.738441944122314</v>
+        <v>3.835742473602295</v>
       </c>
       <c r="J6" t="n">
-        <v>3.636025905609131</v>
+        <v>3.653185606002808</v>
       </c>
       <c r="K6" t="n">
-        <v>4.08707332611084</v>
+        <v>4.065326690673828</v>
       </c>
       <c r="L6" t="n">
-        <v>3.934504938125611</v>
+        <v>3.949174666404724</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>5.578206300735474</v>
+        <v>4.974697351455688</v>
       </c>
       <c r="C7" t="n">
-        <v>5.065945148468018</v>
+        <v>5.196104764938354</v>
       </c>
       <c r="D7" t="n">
-        <v>5.318453550338745</v>
+        <v>5.766578912734985</v>
       </c>
       <c r="E7" t="n">
-        <v>5.029240608215332</v>
+        <v>4.76525616645813</v>
       </c>
       <c r="F7" t="n">
-        <v>4.553429126739502</v>
+        <v>4.497630834579468</v>
       </c>
       <c r="G7" t="n">
-        <v>4.61547327041626</v>
+        <v>4.99564003944397</v>
       </c>
       <c r="H7" t="n">
-        <v>4.850018262863159</v>
+        <v>4.655378580093384</v>
       </c>
       <c r="I7" t="n">
-        <v>4.333375930786133</v>
+        <v>4.707411527633667</v>
       </c>
       <c r="J7" t="n">
-        <v>4.600056171417236</v>
+        <v>4.654553413391113</v>
       </c>
       <c r="K7" t="n">
-        <v>4.321890830993652</v>
+        <v>4.719184160232544</v>
       </c>
       <c r="L7" t="n">
-        <v>4.826608920097351</v>
+        <v>4.893243575096131</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>3.678271770477295</v>
+        <v>4.152894735336304</v>
       </c>
       <c r="C8" t="n">
-        <v>3.902445316314697</v>
+        <v>3.859997510910034</v>
       </c>
       <c r="D8" t="n">
-        <v>3.733494520187378</v>
+        <v>4.609472274780273</v>
       </c>
       <c r="E8" t="n">
-        <v>3.885974168777466</v>
+        <v>3.954977512359619</v>
       </c>
       <c r="F8" t="n">
-        <v>4.330249786376953</v>
+        <v>3.876781463623047</v>
       </c>
       <c r="G8" t="n">
-        <v>4.193710565567017</v>
+        <v>4.00728440284729</v>
       </c>
       <c r="H8" t="n">
-        <v>3.696858882904053</v>
+        <v>4.241657018661499</v>
       </c>
       <c r="I8" t="n">
-        <v>3.824109077453613</v>
+        <v>4.17882513999939</v>
       </c>
       <c r="J8" t="n">
-        <v>4.216182708740234</v>
+        <v>3.80282998085022</v>
       </c>
       <c r="K8" t="n">
-        <v>3.864855289459229</v>
+        <v>4.128958463668823</v>
       </c>
       <c r="L8" t="n">
-        <v>3.932615208625793</v>
+        <v>4.08136785030365</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>3.823533773422241</v>
+        <v>4.027881145477295</v>
       </c>
       <c r="C9" t="n">
-        <v>4.157429456710815</v>
+        <v>3.870121240615845</v>
       </c>
       <c r="D9" t="n">
-        <v>3.619813919067383</v>
+        <v>3.789865493774414</v>
       </c>
       <c r="E9" t="n">
-        <v>4.027180671691895</v>
+        <v>3.810750961303711</v>
       </c>
       <c r="F9" t="n">
-        <v>3.703976631164551</v>
+        <v>3.527221918106079</v>
       </c>
       <c r="G9" t="n">
-        <v>4.025321960449219</v>
+        <v>4.228691339492798</v>
       </c>
       <c r="H9" t="n">
-        <v>3.820542335510254</v>
+        <v>3.797842979431152</v>
       </c>
       <c r="I9" t="n">
-        <v>3.627660512924194</v>
+        <v>3.813800573348999</v>
       </c>
       <c r="J9" t="n">
-        <v>4.362074375152588</v>
+        <v>3.780837774276733</v>
       </c>
       <c r="K9" t="n">
-        <v>4.052808523178101</v>
+        <v>4.02324104309082</v>
       </c>
       <c r="L9" t="n">
-        <v>3.922034215927124</v>
+        <v>3.867025446891785</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>5.044580698013306</v>
+        <v>5.014589548110962</v>
       </c>
       <c r="C10" t="n">
-        <v>5.093624830245972</v>
+        <v>4.81213116645813</v>
       </c>
       <c r="D10" t="n">
-        <v>4.540124893188477</v>
+        <v>5.03154468536377</v>
       </c>
       <c r="E10" t="n">
-        <v>4.939912557601929</v>
+        <v>5.869303941726685</v>
       </c>
       <c r="F10" t="n">
-        <v>5.014325380325317</v>
+        <v>5.151224374771118</v>
       </c>
       <c r="G10" t="n">
-        <v>4.90545916557312</v>
+        <v>5.027555704116821</v>
       </c>
       <c r="H10" t="n">
-        <v>4.522467136383057</v>
+        <v>5.274894237518311</v>
       </c>
       <c r="I10" t="n">
-        <v>5.07111930847168</v>
+        <v>5.422497987747192</v>
       </c>
       <c r="J10" t="n">
-        <v>5.047556161880493</v>
+        <v>4.924830198287964</v>
       </c>
       <c r="K10" t="n">
-        <v>5.231526851654053</v>
+        <v>5.733666658401489</v>
       </c>
       <c r="L10" t="n">
-        <v>4.94106969833374</v>
+        <v>5.226223850250244</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>4.431305885314941</v>
+        <v>5.087500095367432</v>
       </c>
       <c r="C11" t="n">
-        <v>5.454060792922974</v>
+        <v>5.19311261177063</v>
       </c>
       <c r="D11" t="n">
-        <v>4.736093997955322</v>
+        <v>5.506274700164795</v>
       </c>
       <c r="E11" t="n">
-        <v>4.339071750640869</v>
+        <v>4.762264728546143</v>
       </c>
       <c r="F11" t="n">
-        <v>4.258752107620239</v>
+        <v>4.580749750137329</v>
       </c>
       <c r="G11" t="n">
-        <v>4.417757272720337</v>
+        <v>4.684472322463989</v>
       </c>
       <c r="H11" t="n">
-        <v>4.547999143600464</v>
+        <v>4.485005855560303</v>
       </c>
       <c r="I11" t="n">
-        <v>4.979775190353394</v>
+        <v>4.443118333816528</v>
       </c>
       <c r="J11" t="n">
-        <v>4.637693643569946</v>
+        <v>4.458990573883057</v>
       </c>
       <c r="K11" t="n">
-        <v>3.996742486953735</v>
+        <v>4.398752927780151</v>
       </c>
       <c r="L11" t="n">
-        <v>4.579925227165222</v>
+        <v>4.760024189949036</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>3.668874740600586</v>
+        <v>4.41419529914856</v>
       </c>
       <c r="C12" t="n">
-        <v>4.014234781265259</v>
+        <v>4.27057933807373</v>
       </c>
       <c r="D12" t="n">
-        <v>3.751163482666016</v>
+        <v>4.649565935134888</v>
       </c>
       <c r="E12" t="n">
-        <v>3.760507583618164</v>
+        <v>3.857683181762695</v>
       </c>
       <c r="F12" t="n">
-        <v>3.711526393890381</v>
+        <v>4.235673189163208</v>
       </c>
       <c r="G12" t="n">
-        <v>3.586007833480835</v>
+        <v>4.324129104614258</v>
       </c>
       <c r="H12" t="n">
-        <v>3.708491086959839</v>
+        <v>4.009277582168579</v>
       </c>
       <c r="I12" t="n">
-        <v>3.529963731765747</v>
+        <v>3.696115970611572</v>
       </c>
       <c r="J12" t="n">
-        <v>3.844698905944824</v>
+        <v>4.20076584815979</v>
       </c>
       <c r="K12" t="n">
-        <v>3.617441177368164</v>
+        <v>5.072434902191162</v>
       </c>
       <c r="L12" t="n">
-        <v>3.719290971755981</v>
+        <v>4.273042035102844</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>4.109113693237305</v>
+        <v>4.204756259918213</v>
       </c>
       <c r="C13" t="n">
-        <v>3.924290657043457</v>
+        <v>4.207746744155884</v>
       </c>
       <c r="D13" t="n">
-        <v>3.803969144821167</v>
+        <v>4.411203861236572</v>
       </c>
       <c r="E13" t="n">
-        <v>4.776708364486694</v>
+        <v>4.048174858093262</v>
       </c>
       <c r="F13" t="n">
-        <v>3.738868236541748</v>
+        <v>4.045181751251221</v>
       </c>
       <c r="G13" t="n">
-        <v>3.917958736419678</v>
+        <v>4.731207609176636</v>
       </c>
       <c r="H13" t="n">
-        <v>3.831651449203491</v>
+        <v>4.138931751251221</v>
       </c>
       <c r="I13" t="n">
-        <v>4.076056241989136</v>
+        <v>4.068120956420898</v>
       </c>
       <c r="J13" t="n">
-        <v>3.742506980895996</v>
+        <v>4.527528047561646</v>
       </c>
       <c r="K13" t="n">
-        <v>3.468127489089966</v>
+        <v>3.646248817443848</v>
       </c>
       <c r="L13" t="n">
-        <v>3.938925099372864</v>
+        <v>4.20291006565094</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>3.795441865921021</v>
+        <v>3.802830457687378</v>
       </c>
       <c r="C14" t="n">
-        <v>3.972448587417603</v>
+        <v>3.964398860931396</v>
       </c>
       <c r="D14" t="n">
-        <v>4.278034925460815</v>
+        <v>3.928493976593018</v>
       </c>
       <c r="E14" t="n">
-        <v>4.204154968261719</v>
+        <v>4.115993499755859</v>
       </c>
       <c r="F14" t="n">
-        <v>4.094137191772461</v>
+        <v>3.851700067520142</v>
       </c>
       <c r="G14" t="n">
-        <v>4.222867965698242</v>
+        <v>3.825768232345581</v>
       </c>
       <c r="H14" t="n">
-        <v>3.973343849182129</v>
+        <v>4.127960681915283</v>
       </c>
       <c r="I14" t="n">
-        <v>4.623623132705688</v>
+        <v>3.91852068901062</v>
       </c>
       <c r="J14" t="n">
-        <v>3.977776765823364</v>
+        <v>3.886606216430664</v>
       </c>
       <c r="K14" t="n">
-        <v>4.100181102752686</v>
+        <v>3.756953239440918</v>
       </c>
       <c r="L14" t="n">
-        <v>4.124201035499572</v>
+        <v>3.917922592163086</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>4.297435283660889</v>
+        <v>4.071112632751465</v>
       </c>
       <c r="C15" t="n">
-        <v>4.274770021438599</v>
+        <v>4.020236968994141</v>
       </c>
       <c r="D15" t="n">
-        <v>4.358029842376709</v>
+        <v>4.13195013999939</v>
       </c>
       <c r="E15" t="n">
-        <v>4.139166593551636</v>
+        <v>4.036206007003784</v>
       </c>
       <c r="F15" t="n">
-        <v>4.677432537078857</v>
+        <v>3.998308658599854</v>
       </c>
       <c r="G15" t="n">
-        <v>4.333990335464478</v>
+        <v>4.087069988250732</v>
       </c>
       <c r="H15" t="n">
-        <v>4.362543344497681</v>
+        <v>4.039198875427246</v>
       </c>
       <c r="I15" t="n">
-        <v>4.411210060119629</v>
+        <v>4.189795255661011</v>
       </c>
       <c r="J15" t="n">
-        <v>4.364349365234375</v>
+        <v>4.055155754089355</v>
       </c>
       <c r="K15" t="n">
-        <v>4.042463064193726</v>
+        <v>3.87264347076416</v>
       </c>
       <c r="L15" t="n">
-        <v>4.326139044761658</v>
+        <v>4.050167775154113</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>3.901339769363403</v>
+        <v>3.833748340606689</v>
       </c>
       <c r="C16" t="n">
-        <v>4.374834299087524</v>
+        <v>3.817790508270264</v>
       </c>
       <c r="D16" t="n">
-        <v>4.222309112548828</v>
+        <v>3.914531230926514</v>
       </c>
       <c r="E16" t="n">
-        <v>4.284644365310669</v>
+        <v>3.754958629608154</v>
       </c>
       <c r="F16" t="n">
-        <v>4.255674839019775</v>
+        <v>3.939465522766113</v>
       </c>
       <c r="G16" t="n">
-        <v>4.166433095932007</v>
+        <v>4.012270212173462</v>
       </c>
       <c r="H16" t="n">
-        <v>4.131632804870605</v>
+        <v>4.295512676239014</v>
       </c>
       <c r="I16" t="n">
-        <v>4.267759799957275</v>
+        <v>3.890596151351929</v>
       </c>
       <c r="J16" t="n">
-        <v>3.977608442306519</v>
+        <v>4.359342336654663</v>
       </c>
       <c r="K16" t="n">
-        <v>3.959460496902466</v>
+        <v>3.765929222106934</v>
       </c>
       <c r="L16" t="n">
-        <v>4.154169702529908</v>
+        <v>3.958414483070373</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>4.199338436126709</v>
+        <v>4.341389656066895</v>
       </c>
       <c r="C17" t="n">
-        <v>4.108159065246582</v>
+        <v>4.054158449172974</v>
       </c>
       <c r="D17" t="n">
-        <v>4.052011728286743</v>
+        <v>3.8736412525177</v>
       </c>
       <c r="E17" t="n">
-        <v>4.27910041809082</v>
+        <v>4.155887126922607</v>
       </c>
       <c r="F17" t="n">
-        <v>4.55751895904541</v>
+        <v>4.340392589569092</v>
       </c>
       <c r="G17" t="n">
-        <v>4.155049800872803</v>
+        <v>4.347374439239502</v>
       </c>
       <c r="H17" t="n">
-        <v>4.658331394195557</v>
+        <v>4.071103811264038</v>
       </c>
       <c r="I17" t="n">
-        <v>4.039933204650879</v>
+        <v>4.134942531585693</v>
       </c>
       <c r="J17" t="n">
-        <v>4.324880361557007</v>
+        <v>3.877629995346069</v>
       </c>
       <c r="K17" t="n">
-        <v>4.90196681022644</v>
+        <v>4.264595031738281</v>
       </c>
       <c r="L17" t="n">
-        <v>4.327629017829895</v>
+        <v>4.146111488342285</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>3.50905442237854</v>
+        <v>3.61333703994751</v>
       </c>
       <c r="C18" t="n">
-        <v>3.695013523101807</v>
+        <v>3.641262769699097</v>
       </c>
       <c r="D18" t="n">
-        <v>3.490833759307861</v>
+        <v>3.712072849273682</v>
       </c>
       <c r="E18" t="n">
-        <v>3.614015340805054</v>
+        <v>3.593390703201294</v>
       </c>
       <c r="F18" t="n">
-        <v>4.00864315032959</v>
+        <v>3.53753924369812</v>
       </c>
       <c r="G18" t="n">
-        <v>3.735362768173218</v>
+        <v>3.55150294303894</v>
       </c>
       <c r="H18" t="n">
-        <v>3.657121658325195</v>
+        <v>3.55549168586731</v>
       </c>
       <c r="I18" t="n">
-        <v>3.654802560806274</v>
+        <v>3.478697299957275</v>
       </c>
       <c r="J18" t="n">
-        <v>3.570808410644531</v>
+        <v>3.749972343444824</v>
       </c>
       <c r="K18" t="n">
-        <v>3.879873514175415</v>
+        <v>3.713069915771484</v>
       </c>
       <c r="L18" t="n">
-        <v>3.681552910804748</v>
+        <v>3.614633679389954</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>4.017189741134644</v>
+        <v>4.396586894989014</v>
       </c>
       <c r="C19" t="n">
-        <v>5.106400012969971</v>
+        <v>4.073107242584229</v>
       </c>
       <c r="D19" t="n">
-        <v>4.781380891799927</v>
+        <v>4.427160978317261</v>
       </c>
       <c r="E19" t="n">
-        <v>4.772264003753662</v>
+        <v>4.374302387237549</v>
       </c>
       <c r="F19" t="n">
-        <v>4.345431566238403</v>
+        <v>4.279556035995483</v>
       </c>
       <c r="G19" t="n">
-        <v>4.411347627639771</v>
+        <v>4.069117784500122</v>
       </c>
       <c r="H19" t="n">
-        <v>4.642526865005493</v>
+        <v>4.490990400314331</v>
       </c>
       <c r="I19" t="n">
-        <v>4.222006797790527</v>
+        <v>4.192787408828735</v>
       </c>
       <c r="J19" t="n">
-        <v>4.214169502258301</v>
+        <v>4.531881093978882</v>
       </c>
       <c r="K19" t="n">
-        <v>4.356140375137329</v>
+        <v>4.481016159057617</v>
       </c>
       <c r="L19" t="n">
-        <v>4.486885738372803</v>
+        <v>4.331650638580323</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>4.010761260986328</v>
+        <v>3.994318008422852</v>
       </c>
       <c r="C20" t="n">
-        <v>4.09106183052063</v>
+        <v>4.576057910919189</v>
       </c>
       <c r="D20" t="n">
-        <v>4.446327924728394</v>
+        <v>4.008280992507935</v>
       </c>
       <c r="E20" t="n">
-        <v>4.605804681777954</v>
+        <v>4.430152416229248</v>
       </c>
       <c r="F20" t="n">
-        <v>4.097613334655762</v>
+        <v>3.846712589263916</v>
       </c>
       <c r="G20" t="n">
-        <v>4.112306356430054</v>
+        <v>3.891592979431152</v>
       </c>
       <c r="H20" t="n">
-        <v>4.130700588226318</v>
+        <v>4.197773933410645</v>
       </c>
       <c r="I20" t="n">
-        <v>4.177386522293091</v>
+        <v>3.788867950439453</v>
       </c>
       <c r="J20" t="n">
-        <v>4.365504264831543</v>
+        <v>4.094052076339722</v>
       </c>
       <c r="K20" t="n">
-        <v>4.058785915374756</v>
+        <v>3.944451093673706</v>
       </c>
       <c r="L20" t="n">
-        <v>4.209625267982483</v>
+        <v>4.077225995063782</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>4.231237173080444</v>
+        <v>4.451097726821899</v>
       </c>
       <c r="C21" t="n">
-        <v>4.356265783309937</v>
+        <v>4.214729070663452</v>
       </c>
       <c r="D21" t="n">
-        <v>4.08539342880249</v>
+        <v>4.268584728240967</v>
       </c>
       <c r="E21" t="n">
-        <v>4.044429540634155</v>
+        <v>4.10602068901062</v>
       </c>
       <c r="F21" t="n">
-        <v>4.336135625839233</v>
+        <v>4.104024648666382</v>
       </c>
       <c r="G21" t="n">
-        <v>4.060528516769409</v>
+        <v>4.228691816329956</v>
       </c>
       <c r="H21" t="n">
-        <v>3.99120020866394</v>
+        <v>3.975369215011597</v>
       </c>
       <c r="I21" t="n">
-        <v>3.935130596160889</v>
+        <v>4.453091859817505</v>
       </c>
       <c r="J21" t="n">
-        <v>4.138153791427612</v>
+        <v>4.08208441734314</v>
       </c>
       <c r="K21" t="n">
-        <v>4.435830354690552</v>
+        <v>4.211737155914307</v>
       </c>
       <c r="L21" t="n">
-        <v>4.161430501937867</v>
+        <v>4.209543132781983</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>4.237289905548096</v>
+        <v>4.448104619979858</v>
       </c>
       <c r="C22" t="n">
-        <v>4.169342279434204</v>
+        <v>3.877630710601807</v>
       </c>
       <c r="D22" t="n">
-        <v>4.213902711868286</v>
+        <v>3.85568904876709</v>
       </c>
       <c r="E22" t="n">
-        <v>4.004280805587769</v>
+        <v>4.042191028594971</v>
       </c>
       <c r="F22" t="n">
-        <v>3.952296257019043</v>
+        <v>4.258611440658569</v>
       </c>
       <c r="G22" t="n">
-        <v>3.964855194091797</v>
+        <v>3.844718217849731</v>
       </c>
       <c r="H22" t="n">
-        <v>4.206326007843018</v>
+        <v>4.032217741012573</v>
       </c>
       <c r="I22" t="n">
-        <v>4.345193147659302</v>
+        <v>3.970381736755371</v>
       </c>
       <c r="J22" t="n">
-        <v>4.064007520675659</v>
+        <v>3.967390298843384</v>
       </c>
       <c r="K22" t="n">
-        <v>4.189843654632568</v>
+        <v>3.918586015701294</v>
       </c>
       <c r="L22" t="n">
-        <v>4.134733748435974</v>
+        <v>4.021552085876465</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>4.384932994842529</v>
+        <v>4.295512914657593</v>
       </c>
       <c r="C23" t="n">
-        <v>3.9356369972229</v>
+        <v>4.232681751251221</v>
       </c>
       <c r="D23" t="n">
-        <v>4.164918184280396</v>
+        <v>4.021245002746582</v>
       </c>
       <c r="E23" t="n">
-        <v>4.220854043960571</v>
+        <v>4.203758478164673</v>
       </c>
       <c r="F23" t="n">
-        <v>4.542169570922852</v>
+        <v>3.85568904876709</v>
       </c>
       <c r="G23" t="n">
-        <v>4.187207937240601</v>
+        <v>4.212735176086426</v>
       </c>
       <c r="H23" t="n">
-        <v>3.833510160446167</v>
+        <v>4.249635219573975</v>
       </c>
       <c r="I23" t="n">
-        <v>4.324728727340698</v>
+        <v>3.996312379837036</v>
       </c>
       <c r="J23" t="n">
-        <v>3.936925172805786</v>
+        <v>4.550829887390137</v>
       </c>
       <c r="K23" t="n">
-        <v>4.076404333114624</v>
+        <v>3.819785118103027</v>
       </c>
       <c r="L23" t="n">
-        <v>4.160728812217712</v>
+        <v>4.143818497657776</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>3.981804370880127</v>
+        <v>3.994318246841431</v>
       </c>
       <c r="C24" t="n">
-        <v>3.987170457839966</v>
+        <v>4.068121433258057</v>
       </c>
       <c r="D24" t="n">
-        <v>3.860201597213745</v>
+        <v>3.993321418762207</v>
       </c>
       <c r="E24" t="n">
-        <v>4.063601970672607</v>
+        <v>4.174835443496704</v>
       </c>
       <c r="F24" t="n">
-        <v>4.427603721618652</v>
+        <v>3.907549619674683</v>
       </c>
       <c r="G24" t="n">
-        <v>3.889777898788452</v>
+        <v>3.879624843597412</v>
       </c>
       <c r="H24" t="n">
-        <v>3.986205339431763</v>
+        <v>4.379289388656616</v>
       </c>
       <c r="I24" t="n">
-        <v>4.164900302886963</v>
+        <v>4.225699663162231</v>
       </c>
       <c r="J24" t="n">
-        <v>5.356019973754883</v>
+        <v>3.934478998184204</v>
       </c>
       <c r="K24" t="n">
-        <v>3.994192838668823</v>
+        <v>4.043186902999878</v>
       </c>
       <c r="L24" t="n">
-        <v>4.171147847175598</v>
+        <v>4.060042595863342</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>4.266953468322754</v>
+        <v>3.706089019775391</v>
       </c>
       <c r="C25" t="n">
-        <v>4.062911987304688</v>
+        <v>3.456757068634033</v>
       </c>
       <c r="D25" t="n">
-        <v>3.686625719070435</v>
+        <v>3.490665197372437</v>
       </c>
       <c r="E25" t="n">
-        <v>3.669772148132324</v>
+        <v>3.457752704620361</v>
       </c>
       <c r="F25" t="n">
-        <v>3.825372934341431</v>
+        <v>3.692126989364624</v>
       </c>
       <c r="G25" t="n">
-        <v>3.584648132324219</v>
+        <v>3.371982574462891</v>
       </c>
       <c r="H25" t="n">
-        <v>3.928638458251953</v>
+        <v>3.349043846130371</v>
       </c>
       <c r="I25" t="n">
-        <v>4.096110343933105</v>
+        <v>3.401901721954346</v>
       </c>
       <c r="J25" t="n">
-        <v>3.569407939910889</v>
+        <v>3.458750486373901</v>
       </c>
       <c r="K25" t="n">
-        <v>3.637527942657471</v>
+        <v>3.670185089111328</v>
       </c>
       <c r="L25" t="n">
-        <v>3.832796907424927</v>
+        <v>3.505525469779968</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>4.197038173675537</v>
+        <v>4.207747459411621</v>
       </c>
       <c r="C26" t="n">
-        <v>4.109816312789917</v>
+        <v>4.156883239746094</v>
       </c>
       <c r="D26" t="n">
-        <v>4.507123947143555</v>
+        <v>4.578755855560303</v>
       </c>
       <c r="E26" t="n">
-        <v>4.425539970397949</v>
+        <v>4.603688716888428</v>
       </c>
       <c r="F26" t="n">
-        <v>4.720708608627319</v>
+        <v>4.077096700668335</v>
       </c>
       <c r="G26" t="n">
-        <v>4.282406806945801</v>
+        <v>4.219716548919678</v>
       </c>
       <c r="H26" t="n">
-        <v>4.087043762207031</v>
+        <v>4.024238348007202</v>
       </c>
       <c r="I26" t="n">
-        <v>4.209021329879761</v>
+        <v>4.171844005584717</v>
       </c>
       <c r="J26" t="n">
-        <v>4.318718671798706</v>
+        <v>4.2077476978302</v>
       </c>
       <c r="K26" t="n">
-        <v>4.098103284835815</v>
+        <v>4.127960681915283</v>
       </c>
       <c r="L26" t="n">
-        <v>4.295552086830139</v>
+        <v>4.237567925453186</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>4.880002975463867</v>
+        <v>4.503955841064453</v>
       </c>
       <c r="C27" t="n">
-        <v>4.037437438964844</v>
+        <v>4.780216217041016</v>
       </c>
       <c r="D27" t="n">
-        <v>4.577602624893188</v>
+        <v>4.846040487289429</v>
       </c>
       <c r="E27" t="n">
-        <v>4.394556760787964</v>
+        <v>4.260606288909912</v>
       </c>
       <c r="F27" t="n">
-        <v>4.363493919372559</v>
+        <v>4.283545732498169</v>
       </c>
       <c r="G27" t="n">
-        <v>4.525981426239014</v>
+        <v>4.267586946487427</v>
       </c>
       <c r="H27" t="n">
-        <v>4.550619840621948</v>
+        <v>4.667518377304077</v>
       </c>
       <c r="I27" t="n">
-        <v>4.667887926101685</v>
+        <v>4.351363897323608</v>
       </c>
       <c r="J27" t="n">
-        <v>5.346332788467407</v>
+        <v>4.296509265899658</v>
       </c>
       <c r="K27" t="n">
-        <v>4.458311557769775</v>
+        <v>4.859006881713867</v>
       </c>
       <c r="L27" t="n">
-        <v>4.580222725868225</v>
+        <v>4.511634993553161</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>4.125890731811523</v>
+        <v>3.891593456268311</v>
       </c>
       <c r="C28" t="n">
-        <v>4.240745306015015</v>
+        <v>3.851699352264404</v>
       </c>
       <c r="D28" t="n">
-        <v>4.234986782073975</v>
+        <v>3.839731931686401</v>
       </c>
       <c r="E28" t="n">
-        <v>3.915282487869263</v>
+        <v>4.056152820587158</v>
       </c>
       <c r="F28" t="n">
-        <v>3.932377576828003</v>
+        <v>3.903560876846313</v>
       </c>
       <c r="G28" t="n">
-        <v>4.033510208129883</v>
+        <v>4.082083940505981</v>
       </c>
       <c r="H28" t="n">
-        <v>3.839685440063477</v>
+        <v>3.953428030014038</v>
       </c>
       <c r="I28" t="n">
-        <v>4.10080361366272</v>
+        <v>4.143917798995972</v>
       </c>
       <c r="J28" t="n">
-        <v>4.048618316650391</v>
+        <v>4.0920569896698</v>
       </c>
       <c r="K28" t="n">
-        <v>3.794085741043091</v>
+        <v>4.029223918914795</v>
       </c>
       <c r="L28" t="n">
-        <v>4.026598620414734</v>
+        <v>3.984344911575318</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>4.374463319778442</v>
+        <v>4.636600971221924</v>
       </c>
       <c r="C29" t="n">
-        <v>4.87169623374939</v>
+        <v>3.818787336349487</v>
       </c>
       <c r="D29" t="n">
-        <v>4.21553635597229</v>
+        <v>4.045182704925537</v>
       </c>
       <c r="E29" t="n">
-        <v>4.405166625976562</v>
+        <v>4.103027582168579</v>
       </c>
       <c r="F29" t="n">
-        <v>4.613773107528687</v>
+        <v>4.433144807815552</v>
       </c>
       <c r="G29" t="n">
-        <v>3.975023031234741</v>
+        <v>3.742990255355835</v>
       </c>
       <c r="H29" t="n">
-        <v>3.959020614624023</v>
+        <v>3.896579742431641</v>
       </c>
       <c r="I29" t="n">
-        <v>4.414957761764526</v>
+        <v>4.136937141418457</v>
       </c>
       <c r="J29" t="n">
-        <v>4.28978967666626</v>
+        <v>4.106019258499146</v>
       </c>
       <c r="K29" t="n">
-        <v>4.265298366546631</v>
+        <v>4.122974157333374</v>
       </c>
       <c r="L29" t="n">
-        <v>4.338472509384156</v>
+        <v>4.104224395751953</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>4.26453685760498</v>
+        <v>4.158878087997437</v>
       </c>
       <c r="C30" t="n">
-        <v>4.317994594573975</v>
+        <v>3.833748817443848</v>
       </c>
       <c r="D30" t="n">
-        <v>4.231177568435669</v>
+        <v>3.808813810348511</v>
       </c>
       <c r="E30" t="n">
-        <v>3.836243867874146</v>
+        <v>3.869652032852173</v>
       </c>
       <c r="F30" t="n">
-        <v>4.326188802719116</v>
+        <v>3.959410905838013</v>
       </c>
       <c r="G30" t="n">
-        <v>4.093257665634155</v>
+        <v>4.106019735336304</v>
       </c>
       <c r="H30" t="n">
-        <v>4.10912299156189</v>
+        <v>4.099037408828735</v>
       </c>
       <c r="I30" t="n">
-        <v>4.112632751464844</v>
+        <v>3.958414316177368</v>
       </c>
       <c r="J30" t="n">
-        <v>4.039743423461914</v>
+        <v>3.7798912525177</v>
       </c>
       <c r="K30" t="n">
-        <v>4.253767967224121</v>
+        <v>3.877630233764648</v>
       </c>
       <c r="L30" t="n">
-        <v>4.158466649055481</v>
+        <v>3.945149660110474</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>3.698444128036499</v>
+        <v>3.854692220687866</v>
       </c>
       <c r="C31" t="n">
-        <v>3.794252395629883</v>
+        <v>4.056153059005737</v>
       </c>
       <c r="D31" t="n">
-        <v>3.746230602264404</v>
+        <v>3.743987798690796</v>
       </c>
       <c r="E31" t="n">
-        <v>4.078181743621826</v>
+        <v>3.913534164428711</v>
       </c>
       <c r="F31" t="n">
-        <v>3.949959993362427</v>
+        <v>3.900568723678589</v>
       </c>
       <c r="G31" t="n">
-        <v>3.567318677902222</v>
+        <v>4.023241996765137</v>
       </c>
       <c r="H31" t="n">
-        <v>3.609041690826416</v>
+        <v>3.792855978012085</v>
       </c>
       <c r="I31" t="n">
-        <v>3.762648820877075</v>
+        <v>3.901566028594971</v>
       </c>
       <c r="J31" t="n">
-        <v>4.043114900588989</v>
+        <v>3.851699829101562</v>
       </c>
       <c r="K31" t="n">
-        <v>3.872467517852783</v>
+        <v>3.978360652923584</v>
       </c>
       <c r="L31" t="n">
-        <v>3.812166047096253</v>
+        <v>3.901666045188904</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>4.013320922851562</v>
+        <v>4.083081483840942</v>
       </c>
       <c r="C32" t="n">
-        <v>3.798247337341309</v>
+        <v>3.863667011260986</v>
       </c>
       <c r="D32" t="n">
-        <v>4.324606418609619</v>
+        <v>3.6442551612854</v>
       </c>
       <c r="E32" t="n">
-        <v>3.909861326217651</v>
+        <v>3.748974800109863</v>
       </c>
       <c r="F32" t="n">
-        <v>4.014477729797363</v>
+        <v>3.93747091293335</v>
       </c>
       <c r="G32" t="n">
-        <v>4.280453443527222</v>
+        <v>3.914531946182251</v>
       </c>
       <c r="H32" t="n">
-        <v>4.037558794021606</v>
+        <v>3.951433181762695</v>
       </c>
       <c r="I32" t="n">
-        <v>3.755528926849365</v>
+        <v>3.60934853553772</v>
       </c>
       <c r="J32" t="n">
-        <v>4.234971761703491</v>
+        <v>3.629293918609619</v>
       </c>
       <c r="K32" t="n">
-        <v>3.814058542251587</v>
+        <v>3.924505233764648</v>
       </c>
       <c r="L32" t="n">
-        <v>4.018308520317078</v>
+        <v>3.830656218528747</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>4.586359977722168</v>
+        <v>4.225699186325073</v>
       </c>
       <c r="C33" t="n">
-        <v>3.935422658920288</v>
+        <v>4.307481050491333</v>
       </c>
       <c r="D33" t="n">
-        <v>4.142044305801392</v>
+        <v>4.26659083366394</v>
       </c>
       <c r="E33" t="n">
-        <v>4.193667888641357</v>
+        <v>4.449101686477661</v>
       </c>
       <c r="F33" t="n">
-        <v>5.190949440002441</v>
+        <v>4.29451584815979</v>
       </c>
       <c r="G33" t="n">
-        <v>4.352105379104614</v>
+        <v>3.994318008422852</v>
       </c>
       <c r="H33" t="n">
-        <v>4.508822679519653</v>
+        <v>4.428157091140747</v>
       </c>
       <c r="I33" t="n">
-        <v>4.030295848846436</v>
+        <v>3.963894844055176</v>
       </c>
       <c r="J33" t="n">
-        <v>3.925546884536743</v>
+        <v>4.276563882827759</v>
       </c>
       <c r="K33" t="n">
-        <v>4.294479846954346</v>
+        <v>4.127960920333862</v>
       </c>
       <c r="L33" t="n">
-        <v>4.315969491004944</v>
+        <v>4.233428335189819</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>3.860051870346069</v>
+        <v>3.59538459777832</v>
       </c>
       <c r="C34" t="n">
-        <v>3.784373760223389</v>
+        <v>3.645251512527466</v>
       </c>
       <c r="D34" t="n">
-        <v>3.609134435653687</v>
+        <v>3.69511890411377</v>
       </c>
       <c r="E34" t="n">
-        <v>3.901653051376343</v>
+        <v>3.706088781356812</v>
       </c>
       <c r="F34" t="n">
-        <v>3.588460445404053</v>
+        <v>3.895581960678101</v>
       </c>
       <c r="G34" t="n">
-        <v>3.792633533477783</v>
+        <v>3.597378730773926</v>
       </c>
       <c r="H34" t="n">
-        <v>4.061729431152344</v>
+        <v>3.512606859207153</v>
       </c>
       <c r="I34" t="n">
-        <v>3.593374252319336</v>
+        <v>3.853694677352905</v>
       </c>
       <c r="J34" t="n">
-        <v>4.133702993392944</v>
+        <v>3.579427480697632</v>
       </c>
       <c r="K34" t="n">
-        <v>3.854450702667236</v>
+        <v>3.819785356521606</v>
       </c>
       <c r="L34" t="n">
-        <v>3.817956447601318</v>
+        <v>3.690031886100769</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>4.367860078811646</v>
+        <v>4.448104381561279</v>
       </c>
       <c r="C35" t="n">
-        <v>4.828077077865601</v>
+        <v>4.454089164733887</v>
       </c>
       <c r="D35" t="n">
-        <v>5.862506628036499</v>
+        <v>4.638595104217529</v>
       </c>
       <c r="E35" t="n">
-        <v>4.293426275253296</v>
+        <v>4.251630067825317</v>
       </c>
       <c r="F35" t="n">
-        <v>5.049538373947144</v>
+        <v>4.250632762908936</v>
       </c>
       <c r="G35" t="n">
-        <v>4.501418352127075</v>
+        <v>4.44212007522583</v>
       </c>
       <c r="H35" t="n">
-        <v>4.792075872421265</v>
+        <v>4.715871334075928</v>
       </c>
       <c r="I35" t="n">
-        <v>5.554990768432617</v>
+        <v>4.775229930877686</v>
       </c>
       <c r="J35" t="n">
-        <v>4.482070684432983</v>
+        <v>5.66584849357605</v>
       </c>
       <c r="K35" t="n">
-        <v>5.213708162307739</v>
+        <v>5.920846223831177</v>
       </c>
       <c r="L35" t="n">
-        <v>4.894567227363586</v>
+        <v>4.756296753883362</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>3.545430898666382</v>
+        <v>3.414868354797363</v>
       </c>
       <c r="C36" t="n">
-        <v>3.50127387046814</v>
+        <v>3.755955219268799</v>
       </c>
       <c r="D36" t="n">
-        <v>3.555604219436646</v>
+        <v>3.639027118682861</v>
       </c>
       <c r="E36" t="n">
-        <v>3.515498876571655</v>
+        <v>3.534548044204712</v>
       </c>
       <c r="F36" t="n">
-        <v>3.439176082611084</v>
+        <v>3.399907827377319</v>
       </c>
       <c r="G36" t="n">
-        <v>3.37324047088623</v>
+        <v>3.531371116638184</v>
       </c>
       <c r="H36" t="n">
-        <v>3.269679069519043</v>
+        <v>3.265267848968506</v>
       </c>
       <c r="I36" t="n">
-        <v>3.403080701828003</v>
+        <v>3.364004135131836</v>
       </c>
       <c r="J36" t="n">
-        <v>3.330864191055298</v>
+        <v>3.191465616226196</v>
       </c>
       <c r="K36" t="n">
-        <v>3.501910209655762</v>
+        <v>3.233353853225708</v>
       </c>
       <c r="L36" t="n">
-        <v>3.443575859069824</v>
+        <v>3.432976913452149</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>4.23101282119751</v>
+        <v>4.286536693572998</v>
       </c>
       <c r="C37" t="n">
-        <v>4.294426441192627</v>
+        <v>4.142920970916748</v>
       </c>
       <c r="D37" t="n">
-        <v>4.570417404174805</v>
+        <v>4.130952119827271</v>
       </c>
       <c r="E37" t="n">
-        <v>4.009230852127075</v>
+        <v>4.027230739593506</v>
       </c>
       <c r="F37" t="n">
-        <v>4.365471839904785</v>
+        <v>4.209742546081543</v>
       </c>
       <c r="G37" t="n">
-        <v>4.244259595870972</v>
+        <v>4.323437929153442</v>
       </c>
       <c r="H37" t="n">
-        <v>4.286199808120728</v>
+        <v>4.196777582168579</v>
       </c>
       <c r="I37" t="n">
-        <v>4.209594964981079</v>
+        <v>4.294515609741211</v>
       </c>
       <c r="J37" t="n">
-        <v>4.656737565994263</v>
+        <v>5.648119211196899</v>
       </c>
       <c r="K37" t="n">
-        <v>4.577597141265869</v>
+        <v>4.563795328140259</v>
       </c>
       <c r="L37" t="n">
-        <v>4.344494843482972</v>
+        <v>4.382402873039245</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>4.292848825454712</v>
+        <v>4.745309829711914</v>
       </c>
       <c r="C38" t="n">
-        <v>4.094350337982178</v>
+        <v>4.318451404571533</v>
       </c>
       <c r="D38" t="n">
-        <v>4.34156060218811</v>
+        <v>4.409209012985229</v>
       </c>
       <c r="E38" t="n">
-        <v>4.270179033279419</v>
+        <v>4.693811655044556</v>
       </c>
       <c r="F38" t="n">
-        <v>4.881354331970215</v>
+        <v>4.178825378417969</v>
       </c>
       <c r="G38" t="n">
-        <v>4.327269554138184</v>
+        <v>4.090062856674194</v>
       </c>
       <c r="H38" t="n">
-        <v>4.199092149734497</v>
+        <v>4.274577617645264</v>
       </c>
       <c r="I38" t="n">
-        <v>4.034522771835327</v>
+        <v>4.481016874313354</v>
       </c>
       <c r="J38" t="n">
-        <v>4.55190110206604</v>
+        <v>4.30448842048645</v>
       </c>
       <c r="K38" t="n">
-        <v>4.343724489212036</v>
+        <v>4.616654396057129</v>
       </c>
       <c r="L38" t="n">
-        <v>4.333680319786072</v>
+        <v>4.411240744590759</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>3.843348741531372</v>
+        <v>3.744985342025757</v>
       </c>
       <c r="C39" t="n">
-        <v>3.866714000701904</v>
+        <v>3.600371122360229</v>
       </c>
       <c r="D39" t="n">
-        <v>3.893690824508667</v>
+        <v>3.557486295700073</v>
       </c>
       <c r="E39" t="n">
-        <v>4.501765727996826</v>
+        <v>3.52656888961792</v>
       </c>
       <c r="F39" t="n">
-        <v>4.487879276275635</v>
+        <v>3.831753253936768</v>
       </c>
       <c r="G39" t="n">
-        <v>3.823467016220093</v>
+        <v>3.567460775375366</v>
       </c>
       <c r="H39" t="n">
-        <v>3.993111610412598</v>
+        <v>3.751965761184692</v>
       </c>
       <c r="I39" t="n">
-        <v>3.772994995117188</v>
+        <v>3.606355428695679</v>
       </c>
       <c r="J39" t="n">
-        <v>3.558431148529053</v>
+        <v>3.507620811462402</v>
       </c>
       <c r="K39" t="n">
-        <v>3.825607061386108</v>
+        <v>3.569453954696655</v>
       </c>
       <c r="L39" t="n">
-        <v>3.956701040267944</v>
+        <v>3.626402163505554</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>4.196905136108398</v>
+        <v>4.086073160171509</v>
       </c>
       <c r="C40" t="n">
-        <v>4.172704935073853</v>
+        <v>4.363331317901611</v>
       </c>
       <c r="D40" t="n">
-        <v>4.740802526473999</v>
+        <v>4.399235725402832</v>
       </c>
       <c r="E40" t="n">
-        <v>4.470052242279053</v>
+        <v>4.229689121246338</v>
       </c>
       <c r="F40" t="n">
-        <v>4.209331035614014</v>
+        <v>4.331417322158813</v>
       </c>
       <c r="G40" t="n">
-        <v>4.120041370391846</v>
+        <v>4.105021953582764</v>
       </c>
       <c r="H40" t="n">
-        <v>4.672995567321777</v>
+        <v>4.2655930519104</v>
       </c>
       <c r="I40" t="n">
-        <v>4.153158187866211</v>
+        <v>4.307480335235596</v>
       </c>
       <c r="J40" t="n">
-        <v>4.443133592605591</v>
+        <v>4.865987300872803</v>
       </c>
       <c r="K40" t="n">
-        <v>4.131829977035522</v>
+        <v>4.178825378417969</v>
       </c>
       <c r="L40" t="n">
-        <v>4.331095457077026</v>
+        <v>4.313265466690064</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>4.039960145950317</v>
+        <v>4.023240566253662</v>
       </c>
       <c r="C41" t="n">
-        <v>4.58626651763916</v>
+        <v>3.822776079177856</v>
       </c>
       <c r="D41" t="n">
-        <v>4.264676094055176</v>
+        <v>3.875635623931885</v>
       </c>
       <c r="E41" t="n">
-        <v>4.457237720489502</v>
+        <v>3.675171852111816</v>
       </c>
       <c r="F41" t="n">
-        <v>4.075843811035156</v>
+        <v>3.932483434677124</v>
       </c>
       <c r="G41" t="n">
-        <v>3.986417770385742</v>
+        <v>4.029195308685303</v>
       </c>
       <c r="H41" t="n">
-        <v>4.206287384033203</v>
+        <v>4.235672235488892</v>
       </c>
       <c r="I41" t="n">
-        <v>4.417751550674438</v>
+        <v>4.166857242584229</v>
       </c>
       <c r="J41" t="n">
-        <v>4.391708374023438</v>
+        <v>4.338398218154907</v>
       </c>
       <c r="K41" t="n">
-        <v>4.133757829666138</v>
+        <v>4.366315126419067</v>
       </c>
       <c r="L41" t="n">
-        <v>4.255990719795227</v>
+        <v>4.046574568748474</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>4.848820686340332</v>
+        <v>4.308478116989136</v>
       </c>
       <c r="C42" t="n">
-        <v>4.228947639465332</v>
+        <v>4.482014894485474</v>
       </c>
       <c r="D42" t="n">
-        <v>3.919548511505127</v>
+        <v>4.51791787147522</v>
       </c>
       <c r="E42" t="n">
-        <v>4.174556732177734</v>
+        <v>4.483011245727539</v>
       </c>
       <c r="F42" t="n">
-        <v>4.304116010665894</v>
+        <v>4.204755544662476</v>
       </c>
       <c r="G42" t="n">
-        <v>3.942470550537109</v>
+        <v>4.542851686477661</v>
       </c>
       <c r="H42" t="n">
-        <v>4.405951261520386</v>
+        <v>4.590723514556885</v>
       </c>
       <c r="I42" t="n">
-        <v>4.334400415420532</v>
+        <v>4.4371337890625</v>
       </c>
       <c r="J42" t="n">
-        <v>4.064128398895264</v>
+        <v>4.574766635894775</v>
       </c>
       <c r="K42" t="n">
-        <v>4.070673227310181</v>
+        <v>4.476029634475708</v>
       </c>
       <c r="L42" t="n">
-        <v>4.229361343383789</v>
+        <v>4.461768293380738</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>4.312468290328979</v>
+        <v>4.811134576797485</v>
       </c>
       <c r="C43" t="n">
-        <v>4.536280393600464</v>
+        <v>4.799165725708008</v>
       </c>
       <c r="D43" t="n">
-        <v>4.290558099746704</v>
+        <v>4.750296115875244</v>
       </c>
       <c r="E43" t="n">
-        <v>4.605485439300537</v>
+        <v>4.792185068130493</v>
       </c>
       <c r="F43" t="n">
-        <v>4.587382555007935</v>
+        <v>4.662530899047852</v>
       </c>
       <c r="G43" t="n">
-        <v>4.398245334625244</v>
+        <v>4.462067842483521</v>
       </c>
       <c r="H43" t="n">
-        <v>4.530303716659546</v>
+        <v>4.695443391799927</v>
       </c>
       <c r="I43" t="n">
-        <v>4.078006267547607</v>
+        <v>4.434141635894775</v>
       </c>
       <c r="J43" t="n">
-        <v>4.44607400894165</v>
+        <v>4.805149555206299</v>
       </c>
       <c r="K43" t="n">
-        <v>4.638847827911377</v>
+        <v>4.817117929458618</v>
       </c>
       <c r="L43" t="n">
-        <v>4.442365193367005</v>
+        <v>4.702923274040222</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>3.815747261047363</v>
+        <v>4.073107719421387</v>
       </c>
       <c r="C44" t="n">
-        <v>4.08523964881897</v>
+        <v>3.968387842178345</v>
       </c>
       <c r="D44" t="n">
-        <v>4.339741230010986</v>
+        <v>3.902563571929932</v>
       </c>
       <c r="E44" t="n">
-        <v>3.937993764877319</v>
+        <v>4.097043514251709</v>
       </c>
       <c r="F44" t="n">
-        <v>4.089810609817505</v>
+        <v>4.091060400009155</v>
       </c>
       <c r="G44" t="n">
-        <v>3.987152814865112</v>
+        <v>4.048173904418945</v>
       </c>
       <c r="H44" t="n">
-        <v>3.990721702575684</v>
+        <v>3.833747863769531</v>
       </c>
       <c r="I44" t="n">
-        <v>3.871535539627075</v>
+        <v>3.869651794433594</v>
       </c>
       <c r="J44" t="n">
-        <v>4.483017683029175</v>
+        <v>4.107017278671265</v>
       </c>
       <c r="K44" t="n">
-        <v>4.118524789810181</v>
+        <v>4.006285667419434</v>
       </c>
       <c r="L44" t="n">
-        <v>4.071948504447937</v>
+        <v>3.99970395565033</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>4.063898801803589</v>
+        <v>4.252626895904541</v>
       </c>
       <c r="C45" t="n">
-        <v>4.055036306381226</v>
+        <v>4.153891801834106</v>
       </c>
       <c r="D45" t="n">
-        <v>4.034233093261719</v>
+        <v>4.088067531585693</v>
       </c>
       <c r="E45" t="n">
-        <v>4.025208234786987</v>
+        <v>3.896581649780273</v>
       </c>
       <c r="F45" t="n">
-        <v>4.140607595443726</v>
+        <v>3.886606693267822</v>
       </c>
       <c r="G45" t="n">
-        <v>3.816868543624878</v>
+        <v>4.009277820587158</v>
       </c>
       <c r="H45" t="n">
-        <v>3.881903409957886</v>
+        <v>4.17284107208252</v>
       </c>
       <c r="I45" t="n">
-        <v>3.815539598464966</v>
+        <v>3.848706960678101</v>
       </c>
       <c r="J45" t="n">
-        <v>3.935636758804321</v>
+        <v>4.001300096511841</v>
       </c>
       <c r="K45" t="n">
-        <v>3.90455150604248</v>
+        <v>4.007284164428711</v>
       </c>
       <c r="L45" t="n">
-        <v>3.967348384857178</v>
+        <v>4.031718468666076</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>3.854639053344727</v>
+        <v>4.490990400314331</v>
       </c>
       <c r="C46" t="n">
-        <v>4.043658971786499</v>
+        <v>4.315459251403809</v>
       </c>
       <c r="D46" t="n">
-        <v>3.999250888824463</v>
+        <v>4.204754829406738</v>
       </c>
       <c r="E46" t="n">
-        <v>4.186145544052124</v>
+        <v>4.223705768585205</v>
       </c>
       <c r="F46" t="n">
-        <v>4.236151218414307</v>
+        <v>4.245646476745605</v>
       </c>
       <c r="G46" t="n">
-        <v>4.227098226547241</v>
+        <v>4.439128637313843</v>
       </c>
       <c r="H46" t="n">
-        <v>4.307334661483765</v>
+        <v>4.139928340911865</v>
       </c>
       <c r="I46" t="n">
-        <v>3.931569576263428</v>
+        <v>4.211735725402832</v>
       </c>
       <c r="J46" t="n">
-        <v>4.363030195236206</v>
+        <v>4.252628087997437</v>
       </c>
       <c r="K46" t="n">
-        <v>4.26444149017334</v>
+        <v>4.31047248840332</v>
       </c>
       <c r="L46" t="n">
-        <v>4.14133198261261</v>
+        <v>4.283445000648499</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>4.661727428436279</v>
+        <v>5.097368955612183</v>
       </c>
       <c r="C47" t="n">
-        <v>4.130847454071045</v>
+        <v>4.154888868331909</v>
       </c>
       <c r="D47" t="n">
-        <v>4.217087507247925</v>
+        <v>4.150899410247803</v>
       </c>
       <c r="E47" t="n">
-        <v>4.632652997970581</v>
+        <v>4.700429916381836</v>
       </c>
       <c r="F47" t="n">
-        <v>4.17500114440918</v>
+        <v>4.135940074920654</v>
       </c>
       <c r="G47" t="n">
-        <v>4.315857887268066</v>
+        <v>4.589725971221924</v>
       </c>
       <c r="H47" t="n">
-        <v>4.536481142044067</v>
+        <v>4.436137199401855</v>
       </c>
       <c r="I47" t="n">
-        <v>4.150688171386719</v>
+        <v>4.543848514556885</v>
       </c>
       <c r="J47" t="n">
-        <v>4.348222017288208</v>
+        <v>4.583742141723633</v>
       </c>
       <c r="K47" t="n">
-        <v>4.080856084823608</v>
+        <v>4.274569034576416</v>
       </c>
       <c r="L47" t="n">
-        <v>4.324942183494568</v>
+        <v>4.466755008697509</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>4.117532253265381</v>
+        <v>4.517144680023193</v>
       </c>
       <c r="C48" t="n">
-        <v>4.297716856002808</v>
+        <v>4.091059684753418</v>
       </c>
       <c r="D48" t="n">
-        <v>4.156223058700562</v>
+        <v>4.518914937973022</v>
       </c>
       <c r="E48" t="n">
-        <v>4.745292901992798</v>
+        <v>4.27057933807373</v>
       </c>
       <c r="F48" t="n">
-        <v>4.130350589752197</v>
+        <v>4.215726137161255</v>
       </c>
       <c r="G48" t="n">
-        <v>4.336752891540527</v>
+        <v>4.370312929153442</v>
       </c>
       <c r="H48" t="n">
-        <v>4.334079265594482</v>
+        <v>4.368318319320679</v>
       </c>
       <c r="I48" t="n">
-        <v>4.215079784393311</v>
+        <v>4.287534952163696</v>
       </c>
       <c r="J48" t="n">
-        <v>3.937338829040527</v>
+        <v>4.490989923477173</v>
       </c>
       <c r="K48" t="n">
-        <v>4.397603034973145</v>
+        <v>4.292520999908447</v>
       </c>
       <c r="L48" t="n">
-        <v>4.266796946525574</v>
+        <v>4.342310190200806</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>4.536524534225464</v>
+        <v>4.510936260223389</v>
       </c>
       <c r="C49" t="n">
-        <v>4.353523969650269</v>
+        <v>4.437134981155396</v>
       </c>
       <c r="D49" t="n">
-        <v>4.411113262176514</v>
+        <v>4.801160573959351</v>
       </c>
       <c r="E49" t="n">
-        <v>4.224216461181641</v>
+        <v>4.654552698135376</v>
       </c>
       <c r="F49" t="n">
-        <v>4.638270139694214</v>
+        <v>4.64557671546936</v>
       </c>
       <c r="G49" t="n">
-        <v>4.243597030639648</v>
+        <v>4.447107315063477</v>
       </c>
       <c r="H49" t="n">
-        <v>4.197370052337646</v>
+        <v>5.400558233261108</v>
       </c>
       <c r="I49" t="n">
-        <v>4.473671913146973</v>
+        <v>4.548835515975952</v>
       </c>
       <c r="J49" t="n">
-        <v>4.229956388473511</v>
+        <v>4.597704410552979</v>
       </c>
       <c r="K49" t="n">
-        <v>4.724860429763794</v>
+        <v>4.737331867218018</v>
       </c>
       <c r="L49" t="n">
-        <v>4.403310418128967</v>
+        <v>4.67808985710144</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>3.418055057525635</v>
+        <v>3.621315479278564</v>
       </c>
       <c r="C50" t="n">
-        <v>3.689921379089355</v>
+        <v>3.553497314453125</v>
       </c>
       <c r="D50" t="n">
-        <v>3.716429710388184</v>
+        <v>3.672178983688354</v>
       </c>
       <c r="E50" t="n">
-        <v>3.522582054138184</v>
+        <v>3.582419157028198</v>
       </c>
       <c r="F50" t="n">
-        <v>3.642098188400269</v>
+        <v>3.483684301376343</v>
       </c>
       <c r="G50" t="n">
-        <v>3.535494089126587</v>
+        <v>3.744985103607178</v>
       </c>
       <c r="H50" t="n">
-        <v>3.762876987457275</v>
+        <v>3.658215761184692</v>
       </c>
       <c r="I50" t="n">
-        <v>3.605939865112305</v>
+        <v>3.730026006698608</v>
       </c>
       <c r="J50" t="n">
-        <v>3.368243932723999</v>
+        <v>3.519587993621826</v>
       </c>
       <c r="K50" t="n">
-        <v>3.513479471206665</v>
+        <v>3.669187307357788</v>
       </c>
       <c r="L50" t="n">
-        <v>3.577512073516846</v>
+        <v>3.623509740829468</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>4.034356594085693</v>
+        <v>4.250633001327515</v>
       </c>
       <c r="C51" t="n">
-        <v>4.211540937423706</v>
+        <v>4.223705291748047</v>
       </c>
       <c r="D51" t="n">
-        <v>4.399780511856079</v>
+        <v>4.159875869750977</v>
       </c>
       <c r="E51" t="n">
-        <v>4.438016414642334</v>
+        <v>4.05715012550354</v>
       </c>
       <c r="F51" t="n">
-        <v>4.050792932510376</v>
+        <v>4.423171758651733</v>
       </c>
       <c r="G51" t="n">
-        <v>4.205925226211548</v>
+        <v>4.399236679077148</v>
       </c>
       <c r="H51" t="n">
-        <v>4.182235240936279</v>
+        <v>4.325432777404785</v>
       </c>
       <c r="I51" t="n">
-        <v>4.154013872146606</v>
+        <v>4.244648456573486</v>
       </c>
       <c r="J51" t="n">
-        <v>4.149772882461548</v>
+        <v>4.17284107208252</v>
       </c>
       <c r="K51" t="n">
-        <v>4.174688339233398</v>
+        <v>4.27656364440918</v>
       </c>
       <c r="L51" t="n">
-        <v>4.200112295150757</v>
+        <v>4.253325867652893</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4.253394331932068</v>
+        <v>4.294463496208191</v>
       </c>
       <c r="C52" t="n">
-        <v>4.264229640960694</v>
+        <v>4.206617140769959</v>
       </c>
       <c r="D52" t="n">
-        <v>4.294729704856873</v>
+        <v>4.248367257118225</v>
       </c>
       <c r="E52" t="n">
-        <v>4.293749423027038</v>
+        <v>4.194570260047913</v>
       </c>
       <c r="F52" t="n">
-        <v>4.341812953948975</v>
+        <v>4.143927531242371</v>
       </c>
       <c r="G52" t="n">
-        <v>4.197405753135681</v>
+        <v>4.181795945167542</v>
       </c>
       <c r="H52" t="n">
-        <v>4.20822078704834</v>
+        <v>4.217687168121338</v>
       </c>
       <c r="I52" t="n">
-        <v>4.246906709671021</v>
+        <v>4.164373421669007</v>
       </c>
       <c r="J52" t="n">
-        <v>4.290220766067505</v>
+        <v>4.244622569084168</v>
       </c>
       <c r="K52" t="n">
-        <v>4.243613834381104</v>
+        <v>4.24936930179596</v>
       </c>
       <c r="L52" t="n">
-        <v>4.26342839050293</v>
+        <v>4.214579409122467</v>
       </c>
     </row>
   </sheetData>
